--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0016.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0016.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Để tôi lo!</t>
+          <t>Để đó cho tôi!</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Frostbite Tortoise, ta chọn ngươi! Hãy bảo vệ Linghan!</t>
+          <t>Rùa Sương Giá, ta chọn ngươi! Hãy bảo vệ Linghan!</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Hãy nắm lấy cơ hội này...!</t>
+          <t>Nắm lấy cơ hội này...!</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>C-Chúng tôi không sao! Chỉ là cần lấy lại hơi thôi, sau khoảnh khắc điên rồ đó...</t>
+          <t>Chúng ta ổn mà! Chỉ là cần hít thở chút thôi, sau cú đó hơi căng quá…</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Thay vì lo lắng cho chúng tôi, hãy đi kiểm tra bà Linghan có ổn không đi!</t>
+          <t>Thay vì khiến chúng tôi lo lắng, đi kiểm tra bà Linghan có ổn không đi!</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Linghan, cậu thấy thế nào? Có bị thương không? Đau chỗ nào không?</t>
+          <t>Lăng Hàn, cậu thấy thế nào? Có bị thương chỗ nào không? Đau không?</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Cậu nuôi dưỡng nó thật tốt, và thời điểm này không thể hoàn hảo hơn.</t>
+          <t>Cậu nuôi dưỡng nó rất tốt, và thời điểm này không thể hoàn hảo hơn.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Linghan...</t>
+          <t>Lăng Hàn...</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Nhìn Echo của bạn khiến tôi nhớ đến người thân yêu của mình...</t>
+          <t>Nhìn Echo của cậu, ta lại nhớ đến người thân yêu của mình...</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Anh ấy liên tục che chắn cho cả đội bằng một chú Rùa Sương Giá nhỏ bé.</t>
+          <t>Hắn liên tục che chở cả đội bằng một con Frostbite Tortoise bé nhỏ.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Ban đầu, mọi người chế giễu cậu vì chọn một Echo có vẻ yếu ớt. Nhưng cuối cùng, sức mạnh của nó đã khiến tất cả phải im lặng.</t>
+          <t>Lúc đầu, ai cũng chế nhạo cậu ấy vì chọn một Echo có vẻ yếu đuối. Nhưng cuối cùng, sức mạnh của nó đã khiến tất cả phải câm lặng.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Xét cho cùng, sức mạnh của Echo nằm ở tay người sử dụng nó.</t>
+          <t>Dù sao, sức mạnh của Echo nằm trong tay người sử dụng nó.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Tôi hiểu rồi. Trước đây, phán đoán của tôi bị che mờ bởi sức mạnh, chỉ bắt giữ Echoes dựa trên vẻ bề ngoài. Bạn đúng. Bạn luôn đúng.</t>
+          <t>Ra là vậy. Ta đã để sức mạnh che mờ lý trí, bắt giữ những Echo chỉ dựa vào vẻ ngoài. Ngươi nói đúng. Ngươi luôn đúng.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Ông Jingzhu, sao ông lại khóc thế ạ?</t>
+          <t>Ông nội Jingzhu, sao ông lại khóc thế?</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Nhân tiện, cậu giống hệt người thân yêu của tôi đến lạ...</t>
+          <t>À mà này, cậu giống hệt người mà ta quý mến đến lạ...</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Cũng có mũi có mắt, giống thật đấy, hihi.</t>
+          <t>Đều có mũi có mắt, giống thật đấy, hihi.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Nhưng cậu chẳng đẹp trai bằng anh ấy chút nào. Trong mắt tôi, anh ấy là bất khả so sánh—thông thái và dũng cảm vượt bậc.</t>
+          <t>Nhưng cậu chẳng đẹp trai bằng anh ấy tí nào. Trong mắt tớ, anh ấy là người vô song—thông thái và dũng cảm vượt xa mọi giới hạn.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Đ-Đục thủy tinh thể của cậu có vẻ nặng thêm rồi...</t>
+          <t>Bệnh đục thủy tinh thể của cậu... có vẻ nặng thêm rồi...</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Nhanh lên! Giúp cô ấy làm quen lại với cậu đi!</t>
+          <t>Nhanh lên nào! Giúp cô ấy nhớ lại cậu đi!</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Jingzhu... Cậu vừa cầm hoa đấy à?</t>
+          <t>Tinh Châu... Cậu vừa cầm hoa à?</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Ồ đúng rồi! Tôi mải đối phó với lũ Tacet Discord nên đánh rơi chúng ở đâu đó mất rồi.</t>
+          <t>Ừ nhỉ! Lúc đó tớ bận đối phó mấy con Tacet Discord, lỡ làm rơi đâu mất rồi.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Để tôi lấy chúng cho!</t>
+          <t>Để tớ lấy cho cậu!</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Chúng ở ngay đây rồi. Đưa chúng về cho ông Jingzhu thôi!</t>
+          <t>Họ ở ngay đây rồi. Đưa họ về cho ông Jingzhu thôi!</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Đây, Noctemint này dành cho ngươi. Hãy nhận lấy, Linghan. Ngươi sẽ lại trở thành người bạn đồng hành suốt đời của ta chứ?</t>
+          <t>Đây, hoa Noctemint này là của cậu. Hãy nhận lấy đi, Linghan. Liệu cậu có muốn một lần nữa trở thành người bạn đồng hành suốt đời của tớ không?</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>À, mùi Noctemint... thật quen thuộc. Người yêu dấu của tôi thường mang Noctemint về cho tôi. Chỉ cần hít một hơi thôi cũng đủ khiến tinh thần tôi phấn chấn.</t>
+          <t>À, mùi Noctemint... thật thân quen. Người thương của ta thường mang Noctemint về cho ta. Chỉ cần hít một hơi là tinh thần phấn chấn ngay.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hoa, Echoes... đều như nhau cả. Quan trọng là thực tế.</t>
+          <t>Hoa, Tiếng Vọng... tất cả đều như nhau. Thực dụng mới là điều quan trọng.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>V-Vâng! Từ giờ phút này, em sẽ ở bên anh, tận hưởng ánh nắng, trò chuyện... Bất cứ điều gì anh muốn, em sẽ luôn ở bên anh!</t>
+          <t>V-Vâng! Từ giờ phút này, con sẽ ở bên bạn, cùng đón nắng, cùng trò chuyện... Bất cứ điều gì bạn muốn, con sẽ luôn ở đó!</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Miễn là được ở bên cạnh cậu!</t>
+          <t>Chỉ cần được ở bên cạnh cậu là đủ!</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Bởi vì tớ đã hứa với cậu, Linghan. Tớ thề sẽ không bao giờ để cậu một mình, và tớ sẽ giữ lời hứa đó mãi mãi.</t>
+          <t>Bởi vì ta đã hứa với cậu, Linghan. Ta thề sẽ không bao giờ để cậu cô đơn, và ta sẽ giữ lời hứa ấy đến muôn đời.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Nhưng tiếc là ta không thể tắm nắng ở đây.</t>
+          <t>Nhưng tiếc thay, ở đây chúng ta không thể tắm nắng được.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Hãy hộ tống tôi về nhà. Ngồi phơi nắng trước cửa là nơi tôi thấy thoải mái nhất.</t>
+          <t>Hộ tống ta về đi. Ngồi phơi nắng trước cửa nhà mới là nơi ta thấy thoải mái nhất.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Ông Jingzhu, bà Linghan đâu rồi ạ?</t>
+          <t>Ông Tinh Châu, bà Linh Hàn đâu rồi ạ?</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Linh Hàn không được khỏe, nên tôi đã để cô ấy trở về nghỉ ngơi.</t>
+          <t>Lăng Hàn không được khỏe, nên ta đã để cô ấy trở về nghỉ ngơi trước.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Thật nhẹ nhõm khi nghe tin đó! Tôi rất mừng vì cô ấy đã về nhà an toàn.</t>
+          <t>Thật nhẹ cả người khi nghe tin đó! Ta mừng quá, con bé về nhà an toàn rồi.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>À, nhân tiện, mình có cả đống câu hỏi. {PlayerName}, cậu cũng thế phải không?</t>
+          <t>À này, tớ có cả đống câu hỏi đấy. {PlayerName}, cậu cũng thế phải không?</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Yes...</t>
+          <t>Ừ...</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Có thể bạn đã nhận ra: Linghan từng là một Midnight Ranger xuất sắc, đảm nhiệm vị trí đội trưởng đội Vanguard.</t>
+          <t>Có lẽ cậu đã nhận ra rồi: Linghan từng là một Midnight Ranger xuất chúng, từng giữ chức đội trưởng đội Tiền Phong.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Cô ấy không chỉ là đội trưởng của tôi; cô ấy còn là người vợ yêu quý mà tôi đã cùng trải qua bao năm tháng...</t>
+          <t>Cô ấy không chỉ là đội trưởng của ta... mà còn là người vợ yêu dấu, người đã cùng ta trải qua bao năm tháng...</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Là đội trưởng, cô ấy luôn bận rộn, dẫn đầu đội, bảo vệ chúng tôi và dạy chúng tôi các kỹ năng sinh tồn.</t>
+          <t>Là đội trưởng, cô ấy lúc nào cũng bận rộn, luôn dẫn đầu, bảo vệ đội và dạy chúng tôi kỹ năng sinh tồn.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Khi trận chiến leo thang, cô ấy đã vượt qua giới hạn và chịu những vết thương nặng.</t>
+          <t>Khi cuộc chiến ngày càng ác liệt, cô ấy đã vượt qua giới hạn của bản thân và chịu những vết thương nặng.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Sau một chiến thắng lớn, cô ấy cuối cùng cũng đổ bệnh. Tâm trí dần trở nên mơ hồ, khiến ký ức từ từ phai nhạt.</t>
+          <t>Sau một chiến thắng vĩ đại, cuối cùng cô ấy cũng đổ bệnh. Tâm trí dần trở nên mơ hồ, khiến ký ức từ từ phai nhạt.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Cô ấy quên cách đi lại trên đường phố Jinzhou, quên ăn chiếc bánh mũ bảo hiểm yêu thích khi chúng còn nóng, và rồi...</t>
+          <t>Cô ấy quên mất cách đi lại trên những con phố Jinzhou, quên ăn chiếc Bánh Mũ Bảo Bình còn nóng hổi, rồi...</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Cô ấy thậm chí còn quên mất tôi...</t>
+          <t>Cô ấy thậm chí còn quên mất cả tôi...</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Vậy nên đó là lý do cậu đuổi theo bà Linghan à?</t>
+          <t>Ra vậy, nên cậu mới đuổi theo bà Linghan à?</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Cậu muốn ở bên cô ấy như một người đặc biệt.</t>
+          <t>Cậu đang muốn ở bên cạnh cô ấy như một người đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Đúng vậy. Những đồng đội của chúng ta, từng là những thanh niên tràn đầy sức sống, đã hy sinh trong trận chiến, số khác thì qua đời vì bệnh tật.</t>
+          <t>Đúng, cậu nói không sai. Những đồng đội của chúng ta, từng là những thanh niên tràn đầy sức sống, đã ngã xuống trong trận chiến, số khác thì gục ngã vì bệnh tật.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Tôi không khỏi lo sợ rằng một ngày nào đó, nếu cô ấy lấy lại ký ức, cô ấy sẽ cảm thấy cô đơn đến tột cùng... Tôi không thể chịu nổi ý nghĩ đó.</t>
+          <t>Ta không khỏi lo sợ rằng một ngày nào đó, nếu nàng lấy lại ký ức, nàng sẽ cảm thấy cô đơn đến tột cùng... Ta không thể chịu nổi ý nghĩ đó.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Xin lỗi vì đã nhắc đến chuyện buồn. Cảm ơn bạn đã giúp tôi tìm thấy Linghan.</t>
+          <t>Xin lỗi vì đã nhắc đến chuyện buồn. Cảm ơn cậu đã giúp tớ tìm Linghan.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Linghan đã chấp nhận tôi. Thật là vui sướng! Tôi phải cảm thấy hạnh phúc mới được!</t>
+          <t>Lăng Hàn đã chấp nhận ta. Thật là vui sướng! Ta phải cảm thấy hạnh phúc chứ!</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Quá khứ là quá khứ. From now on, tôi sẽ trân trọng từng khoảnh khắc bên Linghan!</t>
+          <t>Quá khứ là quá khứ. Từ giờ trở đi, tớ sẽ trân trọng từng khoảnh khắc bên Linghan!</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Chính xác! Hãy trân trọng từng khoảnh khắc và sống hết mình!</t>
+          <t>Chuẩn luôn! Hãy trân trọng từng khoảnh khắc và sống hết mình đi!</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Hehe, nếu có thời gian, cứ ghé thăm chúng tôi nhé, chúng ta có thể trò chuyện về Echoes thỏa thích.</t>
+          <t>Hehe, nếu có thời gian, cứ ghé qua chỗ bọn mình nhé, chúng ta sẽ tha hồ tám chuyện về Echo.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Tôi không biết phải cảm ơn bạn thế nào cho đủ vì đã giúp giải quyết việc này.</t>
+          <t>Ta không biết phải bày tỏ lòng biết ơn thế nào cho đủ với sự giúp đỡ của ngươi trong chuyện này.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Hơn nữa, thấy bạn khỏe mạnh chắc hẳn đã khiến Linghan yên tâm khi biết những người mà chúng ta đã liều mạng bảo vệ giờ đã trưởng thành tuyệt vời.</t>
+          <t>Với lại, chỉ cần nhìn thấy cậu thôi, Linghan chắc đã yên lòng lắm khi biết những người mà chúng ta từng liều mạng bảo vệ giờ đã trưởng thành tuyệt vời như thế này.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Cảm ơn vì những nỗ lực của bạn. Đây là phần thưởng xứng đáng.</t>
+          <t>Cảm ơn những nỗ lực của cậu. Đây là những gì cậu xứng đáng nhận được.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Ngoài phần bồi thường, lão già này còn có một lời khuyên cho cậu.</t>
+          <t>Ngoài khoản bồi thường, lão già này còn có lời khuyên cho cậu.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Hãy chăm sóc Echoes của bạn thật tốt. Thế giới bên ngoài có thể đầy hiểm nguy, và chúng sẽ rất hữu ích khi cần đến.</t>
+          <t>Hãy chăm sóc Echo của cậu thật tốt. Thế giới ngoài kia đầy hiểm nguy, biết đâu chúng sẽ hữu dụng khi cậu cần đến.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Đợi đã, ai bật cái này lên vậy?</t>
+          <t>Ơ, ai bật cái này lên thế?</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Lần đầu tiên ta thấy màn hình của nó sáng lên...</t>
+          <t>Đây là lần đầu tao thấy màn hình của nó sáng lên...</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Thật sao?! CHO TÔI XEM!</t>
+          <t>Thật á?! CHO TA XEM NÀO!</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Lạ thật—Oh, {PlayerName}! Không ngờ gặp cậu ở đây!</t>
+          <t>Lạ thật đấy—Ô, {PlayerName}! Không ngờ lại gặp cậu ở đây!</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Anh biết tôi à?</t>
+          <t>Cậu biết tớ à?</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Chúng ta đang xem cái gì vậy?</t>
+          <t>Tụi mình đang nhìn cái gì thế?</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Đùa à? Làm sao tôi không nhận ra huyền thoại sống của Học viện chứ!</t>
+          <t>Đùa à? Làm sao ta không nhận ra huyền thoại sống của Học viện được chứ!</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Xem này. Cái máy arcade này đã ở đây từ ngày đầu tiên tôi đi học. Tôi chưa bao giờ thấy nó bật lên.</t>
+          <t>Nhìn này. Cái máy game này đã nằm đây từ ngày đầu mình đi học. Mình chưa bao giờ thấy nó bật lên bao giờ.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Nhưng màn hình của nó hôm nay thực sự đang hoạt động!</t>
+          <t>Nhưng màn hình của nó hôm nay lại sáng đấy!</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Bạn nghiêng người và thấy một dòng chữ hiện ra từ trung tâm màn hình.</t>
+          <t>Bạn nghiêng người và thấy một dòng chữ hiện lên từ trung tâm màn hình.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>"Chú ý toàn thể giảng viên và sinh viên! Chào mừng đến với thế giới Bóng Bàn Ngôi Sao. Đăng nhập bằng Persona Pinball của bạn và bắt đầu một cuộc phiêu lưu hoàn toàn mới!"</t>
+          <t>"Thầy cô và các em học sinh chú ý! Chào mừng đến với thế giới Star Bouncing. Đăng nhập bằng Persona Pinball của các em và bắt đầu một cuộc phiêu lưu hoàn toàn mới!"</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Trông thú vị đấy.</t>
+          <t>Thú vị đấy.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Hmm, ngươi có định thử không?</t>
+          <t>Hm, cậu định thử không?</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Được thôi. Sao lại không?</t>
+          <t>Chắc chắn rồi. Sao lại không?</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>À, {PlayerName}. Cậu làm xong nhanh hơn tôi tưởng đấy. Không bao giờ làm người khác thất vọng nhỉ?</t>
+          <t>À, {PlayerName}. Cậu làm xong nhanh hơn tớ tưởng. Không bao giờ làm người khác thất vọng nhỉ, hả?</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Sao giờ anh lại thấy thất vọng trên khuôn mặt em?</t>
+          <t>Sao mình lại thấy vẻ thất vọng trên mặt cậu lúc này?</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Bà Chủ tịch có thể giải thích tất cả chuyện này không?</t>
+          <t>Muốn giải thích chuyện này không, thưa Chủ tịch?</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Chà, chỉ là một trò chơi nhỏ mình làm khi rảnh rỗi thôi.</t>
+          <t>À, chỉ là trò chơi nhỏ tao làm chơi chơi thôi.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Và đừng lo, cấu trúc bên dưới hoàn toàn an toàn.</t>
+          <t>Và đừng lo, cấu trúc bên trong của nó hoàn toàn an toàn.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Nó chỉ làm lộ ra con người thật của cậu trong chốc lát thôi. Khá thú vị phải không?</t>
+          <t>Nó chỉ tạm thời phơi bày bản ngã ẩn giấu của cậu thôi mà. Khá thú vị phải không?</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>...True.</t>
+          <t>...Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Vậy việc thêm Rainbow Bean Pop Rocks vào game cũng nằm trong kế hoạch của cậu à?</t>
+          <t>Vậy việc thêm kẹo Rainbow Bean Pop Rocks vào trò chơi cũng nằm trong kế hoạch của cậu à?</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Nó hoạt động như một chất xúc tác. Nếu không, trò chơi sẽ trở nên quá nhàm chán và nhạt nhẽo.</t>
+          <t>Nó như một chất xúc tác vậy. Không thì trò chơi này sẽ chán ngắt và vô vị lắm.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Không phải việc của tôi. Anh ấy tự nguyện đăng ký mà.</t>
+          <t>Không phải việc của tao. Ông ấy tự nguyện mà.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Anh ấy tình nguyện đảm bảo mọi thứ được kiểm soát. Tôi thấy hợp lý. Dù sao đó cũng là phát minh của anh ấy mà.</t>
+          <t>Cậu ấy tình nguyện đảm bảo mọi thứ được kiểm soát. Tớ thấy hợp lý mà. Dù sao cũng là phát minh của cậu ấy mà.</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Mornye cũng đã đóng góp một phần nhỏ vào lý thuyết trong giai đoạn đầu, trước khi cô ấy bị chôn vùi dưới núi bài luận của sinh viên...</t>
+          <t>Mornye cũng góp phần xây dựng lý thuyết, dù chỉ là một phần rất nhỏ trong giai đoạn đầu trước khi cô bị chôn vùi dưới núi bài luận của sinh viên...</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Có vẻ như lại là một trò đùa do mấy vị giáo sư ranh mãnh bày ra.</t>
+          <t>Nghe như trò đùa tiếp theo do ban giảng sảo quyệt bày ra.</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Ôi, không cần nặng lời thế chứ. Đó chỉ là một dự án hợp tác học thuật thôi mà.</t>
+          <t>Ui da. Không cần nặng lời thế chứ. Chỉ là hợp tác học thuật thôi mà.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Vậy là cậu làm tất cả những điều này... chỉ để cho tôi thử một lần thôi sao?</t>
+          <t>Vậy là cậu đã làm tất cả những điều này... chỉ để cho tôi được thử sức sao?</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Đúng vậy. Cậu sẽ được trải nghiệm điều gì đó khác biệt—những phản ứng hay tính cách mà bình thường cậu không được thấy.</t>
+          <t>Đúng vậy. Cậu sẽ được trải nghiệm những điều khác biệt—những phản ứng hay tính cách mà bình thường cậu không thấy đâu.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Cậu thấy thế nào? Một bất ngờ nho nhỏ thú vị chứ?</t>
+          <t>Ý cậu thế nào? Một bất ngờ nho nhỏ thú vị chứ?</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Cũng không tệ.</t>
+          <t>Cũng không tệ lắm.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Nếu tôi nói không thì sao?</t>
+          <t>Nếu tớ từ chối thì sao?</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Haha. Tớ mừng là cậu thích nó.</t>
+          <t>Haha. Tao mừng là cậu thích nó.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Hmm... vậy lần sau mình sẽ thử cách khác.</t>
+          <t>Hừm... vậy thì lần sau mình sẽ phải thử cách khác.</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Hy vọng cậu đã tìm thấy chút thú vị khác lạ trong màn tạm nghỉ này, {PlayerName}.</t>
+          <t>Hy vọng cậu đã tìm thấy chút niềm vui bất ngờ trong màn tạm dừng nho nhỏ này, {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Hello, Xiaofang. Hôm nay cậu có vẻ vội vàng. Có chuyện gì vậy?</t>
+          <t>Chào Xiaofang. Hình như cậu đang vội. Hôm nay có chuyện gì thế?</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Shh... Bác Trần Phi... Đừng gọi cháu thế, nhớ không?</t>
+          <t>Suỵt... Chú Trần Bì à... Đừng gọi cháu như thế nữa, nhớ không?</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Ôi, xin lỗi nhé. Lẽ ra tôi nên gọi cậu là Chixia, Tuần Tra Chixia.</t>
+          <t>Ôi, xin lỗi. Tôi nên gọi cậu là Chixia, Tuần Tra Viên Chixia.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Vậy... Cậu nhóc này hẳn là bạn của Patroler Chixia vĩ đại của chúng ta, phải không?</t>
+          <t>Vậy… cậu nhóc này hẳn là bạn của Chixia, tay Tuần tra viên xuất sắc của chúng ta phải không?</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Bác Chenpi, đừng trêu cháu nữa.</t>
+          <t>Chú Trần Bì, chú đừng trêu cháu nữa.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Uncle Chenpi, đây là bạn của cháu, Rover, hehe. Hôm nay cháu dẫn {Male=cậu ấy;Female=cô ấy} đến đây để nhờ giúp đỡ...</t>
+          <t>Chú Trần Bì, đây là bạn của cháu, Rover đấy ạ, hehe. Hôm nay cháu dẫn {Male=him;Female=her} đến đây để nhờ chú giúp đỡ…</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>(Đưa Hòm Sonance cho Chenpi.)</t>
+          <t>Đưa Hòm Sonance cho Chenpi.</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Chà, thứ này khó tìm thật đấy. Tớ đã lùng sục khắp nơi mới kiếm được thứ như này...</t>
+          <t>Wow, thứ này khó tìm thật. Tớ đã lang thang ngoài hoang dã mãi mới kiếm được...</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Hôm nay thật may mắn khi được gặp bạn, Rover.</t>
+          <t>Hôm nay tao thật may mắn khi được gặp cậu, Rover à.</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Trông giống cái hộp, nhưng thực chất là một dạng thực thể năng lượng không có hình dạng vật lý.</t>
+          <t>Trông giống cái hộp, nhưng thực chất là một dạng thực thể năng lượng, không hề có hình dạng vật lý.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Mặt khác... Có thể coi nó như một chiếc hộp theo cách nào đó. Những chiếc hộp thông thường chứa vật phẩm hữu hình, còn Sonance Casket chứa đựng những ghi chép về quá khứ.</t>
+          <t>Mặt khác... Có thể coi đó như một chiếc hộp theo cách nào đó. Những chiếc hộp thông thường chứa vật phẩm, còn Sonance Casket lưu giữ những ký ức quá khứ.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Nói đơn giản thì...</t>
+          <t>Nói đơn giản thôi...</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>À... Chúng là những tàn tích cuối cùng của một thời đại đã qua, bị cuốn trôi bởi dòng chảy khắc nghiệt của lịch sử.</t>
+          <t>À... Họ chính là tàn tích cuối cùng của một thời đại đã qua, bị cuốn phăng bởi dòng chảy nghiệt ngã của lịch sử.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Tại sao?</t>
+          <t>Sao vậy?</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Tất nhiên, tôi sẽ tặng bạn thứ gì đó để đền đáp.</t>
+          <t>Tất nhiên, ta sẽ trả ơn cậu.</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Thẳng thắn mà nói, Sonance Casket không có giá trị tài chính gì cả.</t>
+          <t>Thành thật mà nói, Hòm Sonance chẳng có giá trị tài chính gì cả.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Nhưng với những người như chúng tôi, những kẻ săn tìm di vật, thông tin lưu trữ trong những chiếc Hòm Sonance này là vô cùng quý giá.</t>
+          <t>Nhưng với những kẻ săn lùng di vật như chúng ta, thông tin lưu giữ trong những Chiếc Hòm Sonance này lại vô cùng quý giá.</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Tớ có thể trả cậu bằng Shell Credits hoặc các vật phẩm giá trị khác.</t>
+          <t>Ta có thể trả ngươi bằng Shell Credits, hoặc những vật phẩm có giá trị khác.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Nói ngắn gọn, đây là một thỏa thuận có lợi cho bạn. Tôi sẽ đảm bảo bạn hài lòng với những gì nhận được.</t>
+          <t>Nói ngắn gọn, đây là một cơ hội hời cho cậu. Tôi sẽ đảm bảo cậu hài lòng với những gì nhận được.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Rover, cậu có thể tin bác Chenpi. Bác ấy là chuyên gia thẩm định kho báu nổi tiếng ở Jinzhou, chắc chắn không phải kẻ xấu muốn lừa cậu đâu.</t>
+          <t>Rover, cậu có thể tin tưởng chú Chenpi. Chú ấy là chuyên gia thẩm định kho báu nổi tiếng ở Jinzhou, chắc chắn không phải kẻ xấu muốn lừa cậu đâu.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Hơn nữa, tôi, Chixia, là một Patroller. Nếu hắn dám lừa cậu… Hừ, công lý sẽ trừng phạt hắn.</t>
+          <t>Hơn nữa, tôi, Chixia, là Tuần Phòng viên. Nếu hắn dám lừa cậu… Hừ, công lý sẽ trừng phạt hắn thôi.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Ôi, Chixia... Cậu biết mà, tớ sẽ không bao giờ làm điều như thế đâu...</t>
+          <t>Ôi, Chixia à... Cậu biết mà, tớ sẽ không bao giờ làm chuyện như thế đâu...</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Đùa đấy, bác Trần Phi! Bác tốt bụng thế, không giận đâu nhé?</t>
+          <t>Đùa thôi, chú Trần Bì ơi! Chú tốt bụng thế, không giận đâu nhé?</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Vậy thì thỏa thuận thế này. (Trao Rương Sonance)</t>
+          <t>Vậy là thỏa thuận đã xong. (Đưa Hòm Sonance)</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Tốt quá… Cảm ơn, Rover.</t>
+          <t>Tuyệt... Cảm ơn cậu, Rover.</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Bây giờ, nếu bạn có bất kỳ câu hỏi nào khác, hãy hỏi đi nhé.</t>
+          <t>Giờ nếu còn câu hỏi gì khác, cứ hỏi đi nhé.</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>(Hỏi về việc Chixia đổi tên.)</t>
+          <t>Hỏi về việc Chixia đổi tên.</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>(Ask anh ấy vì sao lại thu thập Sonance Casket.)</t>
+          <t>Hỏi tại sao hắn lại thu thập những chiếc Hòm Sonance.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>(Ask xem anh ấy có thể dạy bạn thẩm định kho báu không.)</t>
+          <t>Hỏi xem ông ấy có thể dạy cậu đánh giá kho báu không.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Tôi không có gì để hỏi.</t>
+          <t>Tao chẳng có gì để hỏi cả.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Haha, ừm... Tôi e là bạn nên hỏi trực tiếp Nhân viên Tuần tra Chixia.</t>
+          <t>Haha, ừ thì... tao e là cậu nên tự hỏi Chixia của Đội Tuần Tra ấy.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Rover, cậu à... Chúng ta có thể không nhắc đến chuyện này không? Cái tên cũ của tớ nghe ngượng lắm, thế thôi...</t>
+          <t>Rover, cậu... Chúng ta có thể không nhắc đến chuyện này không? Tên cũ của tớ ngượng chết đi được, thế thôi...</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Không, tôi không có ý giấu gì bạn cả...</t>
+          <t>Không, tôi không có ý giấu anh điều gì cả...</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Cậu thấy đấy, cái tên "Mã Tiểu Phương" nghe thật nhạt nhẽo. Những anh hùng trong các vở Kịch Anh Hùng mà tôi xem chẳng bao giờ dùng cái tên như thế cả.</t>
+          <t>Cậu thấy đấy, cái tên “Ma Xiaofang” nghe chán chết đi được. Những anh hùng trong các vở kịch anh hùng mà tớ xem chẳng bao giờ dùng cái tên nào ngớ ngẩn thế cả.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Vậy ước mơ của cậu là trở thành anh hùng sao.</t>
+          <t>Vậy ước mơ của cậu là trở thành một anh hùng sao.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Ừ, ta chưa phải là anh hùng đâu, nhưng ta đang cố hết sức.</t>
+          <t>Ừ, tớ chưa phải anh hùng gì đâu, nhưng tớ đang cố hết sức.</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Cậu sẽ là anh hùng của Huanglong, Mã Tiểu Phương à.</t>
+          <t>Cô sẽ là anh hùng của Huanglong đấy, Ma Xiaofang.</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Ngươi sẽ là anh hùng của Huanglong đấy, Xích Hà.</t>
+          <t>Cậu sẽ là anh hùng của Huanglong đấy, Chixia.</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Ôi… Please tha cho tôi đi, Rover.</t>
+          <t>Ôi... Xin cậu đừng nói thế, Rover ơi.</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Thôi được... Vì chúng ta là bạn thân mà, mình sẽ nhượng bộ một chút. Khi chỉ có hai đứa, bạn có thể gọi mình là Mã Tiểu Phương, nhưng đừng làm vậy trước mặt người khác nhé.</t>
+          <t>Thôi được... Vì chúng ta là bạn thân mà, tớ sẽ nhượng bộ một chút. Khi chỉ có hai đứa, cậu có thể gọi tớ là Mã Tiểu Phương, nhưng trước mặt người khác thì đừng làm vậy nhé.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Đúng rồi! Chixia, Chixia... cái tên thật tuyệt vời làm sao! Tôi tự nghĩ ra đấy. Đây là kết tinh của tất cả kinh nghiệm và tri thức của tôi!</t>
+          <t>Đúng rồi! Chixia, Chixia... cái tên nghe thật tuyệt vời! Ta tự nghĩ ra đấy, toàn bộ tri thức và trải nghiệm cuộc đời ta đều dồn vào đó!</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Rover, cứ gọi tôi bằng bất kỳ cái tên nào cũng được, nhưng... Ơm, chỉ cần biết rằng cái tên đó chỉ dành cho riêng chúng ta thôi nhé?</t>
+          <t>Rover, cậu cứ gọi tôi bằng bất cứ cái tên nào cũng được, nhưng... ừm, chỉ cần biết là cái tên đó chỉ dành cho riêng chúng ta thôi nhé?</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Ừ, mình cũng muốn biết. Cậu toàn nghiên cứu quá khứ, nhưng mọi người lại bảo nên hướng tới tương lai, thế nghĩa là sao?</t>
+          <t>Ừ, cháu cũng muốn biết. Chú toàn nghiên cứu về quá khứ, nhưng mọi người vẫn bảo nên hướng về phía trước, thế là sao ạ?</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Ừ, tôi cũng muốn biết. Sao chú Chenpi lại háo hức sưu tầm Sonance Casket thế? Những... Mảnh dữ liệu quá khứ ấy, chúng có quan trọng đến vậy sao?</t>
+          <t>Ừ, cháu cũng muốn biết. Sao chú Chenpi lại mê sưu tầm những chiếc Hòm Sonance thế? Những... mảnh dữ liệu của quá khứ ấy, chúng có quan trọng đến vậy sao?</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Quá khứ đã ảnh hưởng đến hiện tại và tương lai, bởi mọi thứ chúng ta thấy đều đã thay đổi rất nhiều qua nhiều năm.</t>
+          <t>Quá khứ đã ảnh hưởng đến hiện tại và cả tương lai, bởi mọi thứ chúng ta thấy đều đã thay đổi rất nhiều qua bao năm tháng.</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Những hạt giống của ngày hôm qua sẽ đâm chồi nảy lộc thành những bông hoa của ngày mai. Nếu thiếu hiểu biết về lịch sử, làm sao chúng ta có thể bàn luận về tương lai?</t>
+          <t>Hạt giống của ngày hôm qua sẽ đâm chồi nở hoa vào ngày mai. Nếu không hiểu biết về lịch sử, làm sao chúng ta có thể bàn luận về tương lai?</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Quá khứ là lời nhắc nhở về cội nguồn của chúng ta, đảm bảo rằng ta không đánh mất ý chí ban đầu giữa dòng chảy lịch sử cuồn cuộn.</t>
+          <t>Quá khứ là lời nhắc nhở về cội nguồn, để ta không đánh mất bản ngã giữa dòng chảy dữ dội của lịch sử.</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>À... I see. Nghe thật ngầu. Cảm ơn chú Chenpi nhé.</t>
+          <t>À… tao hiểu rồi. Nghe hay đấy. Cảm ơn chú Chenpi nhé.</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Không có gì.</t>
+          <t>Không có gì đâu.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>À đúng rồi. Bác Trần Phi là người thẩm định kho báu giỏi nhất thị trấn.</t>
+          <t>À phải rồi. Bác Chenpi là người thẩm định kho báu giỏi nhất thị trấn đấy.</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Cảm ơn lời khen, Chixia. Ở Jinzhou có rất nhiều người tài năng, và tôi còn lâu mới nằm trong số giỏi nhất.</t>
+          <t>Cảm ơn lời khen của em, Chixia. Ở Jinzhou có rất nhiều người tài năng, và tôi còn lâu mới nằm trong số đó.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Tôi không giỏi bằng cô ấy chút nào. Giới trẻ ngày nay thực sự tài năng.</t>
+          <t>Ta không giỏi bằng cô ấy. Mấy đứa trẻ bây giờ tài thật đấy.</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Ui, nói đến chuyện đó, lâu rồi mình không thấy Youhu đâu. Hy vọng cô ấy không gặp rắc rối gì nữa...</t>
+          <t>À, nói đến đó, lâu rồi mình không thấy Youhu đâu. Hy vọng cô ấy không gặp rắc rối gì nữa...</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Nếu bạn tìm thấy thêm Sonance Casket nào, hãy cân nhắc bán cho tôi nhé.</t>
+          <t>Nếu cậu tìm thấy thêm Sonance Casket nào, hãy cân nhắc bán cho tôi nhé.</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Đừng lo, tiền công sẽ xứng đáng với công sức của cậu. Tôi không keo kiệt khi nói đến tiền đâu.</t>
+          <t>Đừng lo, tiền công sẽ xứng đáng với công sức của cậu. Tớ không keo kiệt đâu mà.</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Hello! Chào mừng đến với chi nhánh Jinzhou của Pioneer Association!</t>
+          <t>Xin chào! Chào mừng đến với chi nhánh Jinzhou của Hiệp hội Pioneer!</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Chắc hẳn cậu là Rover?</t>
+          <t>Chắc cậu là Rover?</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Sao cậu biết?</t>
+          <t>Sao cậu biết được?</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Đúng vậy.</t>
+          <t>Đúng, tôi đây.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Trụ sở chính đã gửi lời mời đến ngươi. Hãy cân nhắc gia nhập Hiệp Hội Pioneer!</t>
+          <t>Trụ sở chính đã gửi lời mời đến cậu. Hãy cân nhắc gia nhập Hiệp Hội Tiên Phong nhé!</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Hãy dùng đôi chân của chính mình để đo đạc hành tinh, và tận mắt chứng kiến những nền văn minh.</t>
+          <t>Đo đạc hành tinh bằng đôi chân của chính mình, và chứng kiến những nền văn minh qua đôi mắt của chính ngươi.</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Hội Tiên Phong?</t>
+          <t>Hiệp hội Tiên Phong à?</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Khám phá thế giới?</t>
+          <t>Khám phá thế giới sao?</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Cho phép tôi giới thiệu ngắn gọn.</t>
+          <t>Để tôi giới thiệu sơ lược.</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Đội ngũ của chúng tôi bao gồm những nhà báo, nhà văn, nhiếp ảnh gia và nhà thám hiểm hàng đầu từ khắp nơi trên thế giới.</t>
+          <t>Đội ngũ của chúng ta gồm những nhà báo, nhà văn, nhiếp ảnh gia và nhà thám hiểm hàng đầu từ khắp nơi trên thế giới.</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Tôi có thể nhận được gì?</t>
+          <t>Tôi được lợi gì từ chuyện này?</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Tôi đồng ý.</t>
+          <t>Mình vào nhé.</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Những Người Tiên Phong của chúng ta kiếm tiền từ việc nộp báo cáo, cộng thêm kinh phí chuyên dụng cho các kế hoạch thám hiểm được Hiệp Hội phê duyệt.</t>
+          <t>Các Tiên Phong của chúng ta kiếm được tiền từ việc nộp báo cáo, cộng thêm khoản tài trợ đặc biệt từ Hiệp Hội cho những kế hoạch thám hiểm được phê duyệt.</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Tôi đồng ý.</t>
+          <t>Mình vào nhé.</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Tuyệt! Tôi sẽ thiết lập hồ sơ cho bạn ngay. Bạn có thể kiểm tra tiến trình khám phá của mình trên Terminal bất cứ lúc nào.</t>
+          <t>Tuyệt vời! Tớ sẽ thiết lập hồ sơ cho cậu ngay. Sau này cậu có thể kiểm tra tiến trình khám phá của mình trên Thiết bị đầu cuối bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Và... xong rồi! From now on, Rover, cậu là thành viên của Pioneer Association. Cậu giờ giống như người nhà của tôi vậy!</t>
+          <t>Và... xong rồi! Từ giờ, Rover à, cậu chính thức là thành viên của Hiệp Hội Tiên Phong. Cũng coi như là gia đình mình rồi đấy!</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Khách hàng mới mua một tặng một giảm 50%!</t>
+          <t>Khách hàng mới mua một tặng một giảm 50% nhé!</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Số mới nhất à?</t>
+          <t>Vấn đề mới nhất à?</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Đăng ký podcast?</t>
+          <t>Đăng ký Podcast?</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Thú bông?</t>
+          <t>Gấu bông à?</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Lần này tôi xin phép.</t>
+          <t>Lần này ta xin phép không tham gia.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Thực ra chúng tôi xuất bản hai loại tạp chí. &lt;i&gt;Wutherium Geographic&lt;/i&gt; dành cho độc giả phổ thông, và &lt;i&gt;Post-Lament Anthropocene&lt;/i&gt; dành cho giới học thuật.</t>
+          <t>Thực ra chúng tôi xuất bản hai tạp chí. &lt;i&gt;Wutherium Địa Lý&lt;/i&gt; dành cho độc giả phổ thông, và &lt;i&gt;Kỷ Nhân Sinh Hậu Lời Than&lt;/i&gt; dành cho giới học thuật.</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Nếu bạn quan tâm đến việc đăng ký tạp chí của chúng tôi, hãy nói với tôi ngay và chúng tôi sẽ gửi những số mới nhất đến tận nhà bạn mỗi tháng!</t>
+          <t>Nếu cậu muốn đăng ký tạp chí của chúng tớ, nói ngay đi và chúng tớ sẽ gửi số mới nhất đến tận nhà mỗi tháng!</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Với đa dạng chương trình từ tin tức, âm nhạc đến khoa học, luôn có thứ gì đó dành cho tất cả mọi người.</t>
+          <t>Với đủ thể loại chương trình từ tin tức, âm nhạc đến khoa học, luôn có thứ gì đó dành cho tất cả mọi người.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Kênh Insider cập nhật những cuộc thám hiểm đang diễn ra bởi các phóng viên ký hợp đồng và các nhà thám hiểm dày dạn kinh nghiệm.</t>
+          <t>Kênh Nội Bộ cập nhật những cuộc thám hiểm đang diễn ra do các phóng viên ký hợp đồng và những nhà thám hiểm kỳ cựu thực hiện.</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Hãy cho tôi biết nếu bạn muốn đăng ký!</t>
+          <t>Báo cho tớ nếu cậu muốn đăng ký nhé!</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Ôi, thú nhồi bông Gulpuff hết hàng mất rồi... Cậu muốn tớ đặt trước một con không?</t>
+          <t>Ôi, Gulpuff bông hết hàng rồi... Cậu muốn tớ đặt trước một con không?</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Dù sao đi nữa, bạn luôn có thể tìm kiếm sự trợ giúp trên hành trình của mình. Hiệp Hội Pioneer sẽ luôn ở bên bạn vượt qua mọi trở ngại!</t>
+          <t>Dù sao đi nữa, cậu luôn có thể tìm kiếm sự trợ giúp trên hành trình của mình. Hiệp hội Pioneer sẽ luôn ở đây để hỗ trợ cậu vượt qua mọi trở ngại!</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Cậu đến rồi.</t>
+          <t>Cậu đã đến rồi.</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Tôi đã ở đây đợi bạn.</t>
+          <t>Ta đã đợi cậu ở đây.</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Chẳng phải chúng ta vừa đánh nhau sao?</t>
+          <t>Chẳng phải tụi mình vừa đánh nhau xong à?</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>(Something's not right... Giống như hắn không nhớ gì về trận chiến của chúng ta.)</t>
+          <t>Có gì đó không ổn... Hắn như không nhớ gì về trận chiến của chúng ta.</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Hiện tại, bạn có thể gọi tôi là Gatekeeper. Tên tôi không quan trọng—điều quan trọng là cánh cổng này.</t>
+          <t>Hiện tại, cậu có thể gọi ta là Người Gác Cổng. Tên ta không quan trọng—điều quan trọng là cánh cổng này.</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tôi nhận ra cánh cổng này.</t>
+          <t>Ta nhận ra cánh cổng này.</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Bạn biết về Somnoire chứ? Đó là nơi lưu trữ tất cả những giấc mơ, ký ức và cảm xúc của Solaris-3.</t>
+          <t>Ngươi biết về Somnoire chứ? Đó là nơi lưu giữ mọi giấc mơ, ký ức và cảm xúc của Solaris-3.</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Nó biết hương vị của viên kẹo yêu thích của một đứa trẻ và những kế hoạch điên rồ của một kẻ độc tài. Nó hiểu rõ vẻ đẹp và bóng tối ẩn giấu trong tiềm thức của sự sống.</t>
+          <t>Nó biết hương vị kẹo yêu thích của một đứa trẻ và những kế hoạch điên rồ của một kẻ độc tài. Nó hiểu rõ vẻ đẹp và bóng tối ẩn sâu trong tiềm thức cuộc sống.</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Nói cách khác, nó lưu giữ giấc mơ của mọi người, được ghi lại mãi mãi.</t>
+          <t>Nói cách khác, nó lưu giữ giấc mơ của tất cả mọi người, được ghi lại vĩnh viễn.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Sao còn đợi tôi làm gì?</t>
+          <t>Sao cậu lại đợi tớ?</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Somnoire ghi lại mọi thứ về hành tinh của chúng ta, và sự hiện diện của bạn là chìa khóa để duy trì hoạt động trơn tru.</t>
+          <t>Somnoire ghi lại mọi thứ về hành tinh này, và sự hiện diện của ngươi là chìa khóa để duy trì hoạt động trơn tru của nó.</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Điều đó chẳng có gì mới với tôi.</t>
+          <t>Chuyện đó với ta chẳng có gì mới mẻ cả.</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tôi biết mà, tôi là Dreamwalker.</t>
+          <t>Tôi biết, tôi là Dreamwalker.</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>...Vậy là cậu nhớ nơi này?</t>
+          <t>...Vậy cậu vẫn nhớ nơi này à?</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Trước khi bạn thức tỉnh, có thứ không nên tồn tại đã xâm nhập vào Somnoire.</t>
+          <t>Trước khi ngươi thức tỉnh, đã có thứ không nên tồn tại xâm nhập vào Somnoire.</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Giờ đây, Somnoire đang hỗn loạn, và sự trợ giúp của bạn rất cần thiết để khôi phục sự ổn định—Chờ đã, có gì đó không ổn…</t>
+          <t>Giờ thì Somnoire đang hỗn loạn, và sự trợ giúp của cậu rất cần thiết để khôi phục sự ổn định—Đợi đã, có gì đó không ổn…</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Lũ quái vật trong đó không khó đánh đến thế đâu.</t>
+          <t>Những con quái vật trong đó không khó đánh đến thế.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Cậu có vẻ bình tĩnh đấy. Tốt. Điều đó có nghĩa là tác động của Somnoire chưa ảnh hưởng đến cậu.</t>
+          <t>Cậu bình tĩnh đấy. Tốt. Điều đó có nghĩa là tác dụng của Somnoire chưa ảnh hưởng đến cậu.</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Cậu tiếp tục cố gắng nhé?</t>
+          <t>Cứ thế mà làm tốt lên, được không?</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Chà, khu vực này đã được dọn dẹp gọn gàng rồi.</t>
+          <t>Ờ, dọn dẹp khu này sạch sẽ nhỉ.</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Như bạn có thể đã nhận thấy, kích thước của Somnoire gần như không thể hình dung được. Đây mới chỉ là phần nổi của tảng băng,</t>
+          <t>Như anh đã thấy, kích thước của Somnoire gần như không thể tưởng tượng nổi. Đây mới chỉ là phần nổi của tảng băng thôi.</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Chúng ta vẫn còn nhiều việc phải làm nếu muốn ngăn Tacet Discord thoát ra lần nữa.</t>
+          <t>Vẫn còn rất nhiều việc phải làm nếu chúng ta muốn ngăn Tacet Discord thoát ra lần nữa.</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Tôi sẽ thường xuyên đến đây.</t>
+          <t>Mình sẽ thường xuyên ghé qua đây.</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Đừng quên phần thưởng cậu đã hứa với tớ nhé.</t>
+          <t>Đừng quên phần thưởng mà cậu đã hứa với tớ.</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Tôi biết cậu không phải loại người chỉ ngồi nhìn đâu.</t>
+          <t>Tôi biết cậu không phải loại người ngồi yên nhìn đâu.</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Tất nhiên, tôi không quên phần thưởng đã hứa với cậu đâu.</t>
+          <t>Tất nhiên, ta không quên phần thưởng đã hứa với cậu.</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Tạm thời kết thúc ở đây đã. Lần sau, chúng ta có thể cùng nhau khám phá sâu hơn vào Khu Vực Ký Ức.</t>
+          <t>Chúng ta tạm dừng ở đây thôi. Lần sau, ta sẽ cùng nhau khám phá sâu hơn vào các Vùng Ký Ức nhé.</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>…Nhưng khi ngày đó đến, có lẽ "bản thân thật" của tôi sẽ lên nắm quyền, cậu nghĩ sao?</t>
+          <t>…Nhưng khi ngày đó đến, biết đâu "bản thân thật" của ta sẽ là người nắm quyền, cậu nghĩ sao?</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Như mọi khi, thật ấn tượng…</t>
+          <t>Như mọi khi… thật ấn tượng.</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Có bạn ở đây, tôi tin chắc chúng ta có thể khôi phục Somnoire về trạng thái bình thường.</t>
+          <t>Có cậu ở đây, ta tin chắc có thể đưa Somnoire trở lại trạng thái bình thường.</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Bạn cần tôi làm gì?</t>
+          <t>Cậu cần tớ làm gì không?</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Tôi chưa thể giải thích thêm cho bạn ngay bây giờ. Không phải trước khi bạn lấy lại ký ức của mình.</t>
+          <t>Tôi chưa thể giải thích thêm cho cậu bây giờ. Trước khi cậu lấy lại ký ức đã.</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Somnoire cần những ký ức và trải nghiệm chân thật, và tôi không nên can thiệp vào chúng.</t>
+          <t>Somnoire cần những ký ức và trải nghiệm chân thật, ta không nên can thiệp vào chúng.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Ít nhất giờ bạn đã biết những cánh cổng này giống như Tacet Field. Tacet Discord có thể thoát ra từ đó.</t>
+          <t>Ít nhất giờ cậu cũng biết những cánh cổng này giống như Tổ Tacet vậy. Tacet Discord có thể thoát ra từ đó.</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Nếu bạn giúp chúng tôi sửa chữa Somnoire, có thể ngăn chặn thêm Tacet Discord xuất hiện. Coi như là xua tan một Tacet Field.</t>
+          <t>Nếu cậu giúp chúng tôi sửa chữa Somnoire, có thể chúng ta sẽ ngăn chặn được thêm Tacet Discord xuất hiện. Coi như là xua tan một Tổ Tacet vậy.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Dù cậu không hỏi, tớ vẫn sẽ làm thôi.</t>
+          <t>Dù cậu không nhờ, tôi vẫn sẽ làm thôi.</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Tôi sẽ cân nhắc nếu phần thưởng hậu hĩnh.</t>
+          <t>Nếu phần thưởng hậu hĩnh, mình sẽ cân nhắc.</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Đúng vậy, cậu lúc nào cũng thế. Có lẽ vì thế mà cánh cổng đã chọn cậu.</t>
+          <t>Ừ, cậu lúc nào cũng thế. Có lẽ chính vì vậy mà cánh cổng đã chọn cậu.</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Đúng, cậu vẫn luôn như thế. Nhưng đừng lo, mình đảm bảo là họ sẽ như vậy.</t>
+          <t>Ừ, cậu lúc nào cũng thế. Nhưng đừng lo, ta đảm bảo chúng sẽ như vậy.</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Thời gian không chờ đợi. Vào trong thôi nào.</t>
+          <t>Thời gian đang trôi đấy. Vào trong thôi.</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Những Tacet Discord đang thoát ra từ Cánh Cổng...</t>
+          <t>Tacet Discord đang tràn ra từ Cánh Cổng...</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Tình hình bên trong Somnoire chắc còn tồi tệ hơn tôi nghĩ.</t>
+          <t>Tình hình bên trong Somnoire còn tồi tệ hơn tao tưởng nhiều.</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Này! Long time no see, {PlayerName}. Mọi chuyện thế nào?</t>
+          <t>Ê! Lâu rồi không gặp, {PlayerName}. Khỏe không?</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Đừng lo! Chuyện nhỏ thôi mà, thật đấy. Chắc chắn không to tát bằng việc lao vào mấy cái token đó đâu.</t>
+          <t>Đừng lo! Chuyện nhỏ thôi mà, thật đấy. Chứ còn không to tát bằng việc lao vào mấy cái thẻ ấy.</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Vậy sao? Thế này nhé, gã lái xe tốc độ Jinzhou này sẽ đưa cậu đi trải nghiệm ẩm thực tại Nhà hàng Dì Panhua nhé?</t>
+          <t>Vậy, cậu thấy sao? Để Jinzhou Speedster này dẫn cậu đi trải nghiệm ẩm thực ở quán cô Panhua nhé?</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Món mao thái cô ấy nấu là một vụ nổ vị cay nồng! Chỉ một ngụm thôi cũng đủ khiến bạn cảm nhận được sự phấn khích thấm vào tận xương!</t>
+          <t>Món Mão Thái nàng nấu cay nồng, đậm đà! Một ngụm thôi là đủ khiến cậu cảm nhận được hơi nóng lan tỏa trong xương!</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ừm, nghe có vẻ cay đúng như ta tưởng tượng.</t>
+          <t>Được rồi, nghe cay đúng như tao đoán.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Nơi nào có đồ ăn ngon, nơi đó có tôi.</t>
+          <t>Nơi nào có đồ ăn ngon, nơi đó có tao.</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Tuyệt! Khi nào chúng ta đi?</t>
+          <t>Tuyệt! Khi nào thì mình đi?</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Không ngờ ngươi cũng là một tín đồ ẩm thực. Lần tới khi đi tuần tra mà tìm được thứ gì ngon, ta sẽ chia sẻ cho ngươi nếm thử.</t>
+          <t>Không ngờ cậu cũng là dân sành ăn. Lần sau đi tuần tra, nếu tìm được gì ngon, nhất định sẽ để dành cho cậu một miếng.</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Vậy là chúng ta hẹn hò nhé?</t>
+          <t>Vậy là chúng ta hẹn hò rồi nhé?</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Hẹn gặp ở Nhà Hàng Panhua trên Phố Ẩm Thực nhé. Còn về thời gian thì báo cho tôi trước khi bạn sẵn sàng.</t>
+          <t>Gặp nhau ở Nhà hàng Panhua trên Phố Ẩm Thực nhé. Còn giờ giấc thì báo mình trước khi cậu sẵn sàng.</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Mình sẽ háo hức chờ tin từ cậu!</t>
+          <t>Tôi sẽ háo hức chờ tin từ cậu nhé!</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Và chúng ta đã đến nơi. Đây chính là &lt;color=Highlight&gt;Bộ Tổng hợp&lt;/color&gt; mà chú Wei đã nhắc đến.</t>
+          <t>Và chúng ta đã đến nơi rồi. Đây chính là &lt;color=Highlight&gt;Bộ tổng hợp&lt;/color&gt; mà chú Wei đã nhắc đến.</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Tôi có một số nguyên liệu tổng hợp ở đây. Cứ thử đi.</t>
+          <t>Tao có mấy nguyên liệu tổng hợp ở đây. Cứ thử dùng đi.</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Nghe qua có vẻ hơi phức tạp, nhưng khi cậu thực hành thử, cậu sẽ nhanh chóng nắm bắt được thôi.</t>
+          <t>Nghe qua có vẻ hơi phức tạp, nhưng khi bắt tay vào làm, cậu sẽ nắm được ngay thôi.</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Cậu thấy thế nào? Khá tiện tay phải không?</t>
+          <t>Cảm giác thế nào? Khá lợi hại phải không?</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Công nghệ ngày càng hiện đại, cuộc sống ở đây cũng trở nên dễ dàng hơn.</t>
+          <t>Công nghệ ngày càng hiện đại, cuộc sống ở đây cũng nhẹ nhàng hơn nhiều.</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Nhưng mà mình cũng tò mò. Nếu tụi mình tập hợp mọi người lại lần nữa và bảo họ mang món ăn quý nhất ra, cậu nghĩ lần này họ sẽ đem gì nhỉ?</t>
+          <t>Nhưng ta cũng hơi tò mò. Nếu ta tập hợp mọi người lại lần nữa và bảo họ mang ra món ăn quý nhất của mình, lần này họ sẽ đem gì nhỉ?</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Ôi, hơi quá tay rồi. Nhanh quay lại quán của Dì Panhua thôi! Ai ngờ nấu một món ăn lại phức tạp thế này...</t>
+          <t>Ôi, hơi quá tay rồi. Nhanh quay lại quán dì Panhua thôi! Ai ngờ nấu một món ăn lại phức tạp thế này...</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Sau khi trở về nhà hàng, bạn và Chixia kể lại toàn bộ câu chuyện cho Panhua và chia sẻ công thức chính hiệu của món Essence Medley Soup với cô ấy.</t>
+          <t>Trở lại nhà hàng, bạn và Chixia kể lại toàn bộ câu chuyện cho Panhua và chia sẻ công thức chính hiệu của món Essence Medley Soup với cô ấy.</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Dì Panhua, để cháu và {PlayerName} thử sức cùng nhau được không ạ?</t>
+          <t>Dì Panhua, để cháu và {PlayerName} thử làm cùng nhau được không ạ?</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Hoàn toàn đồng ý.</t>
+          <t>Đồng ý hoàn toàn.</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Chúng ta sẽ không biết nó ngon thế nào cho đến khi thử.</t>
+          <t>Chúng ta sẽ không biết mùi vị ra sao cho đến khi thử.</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Sau một hồi nỗ lực, bạn đã thành công chế biến món Súp Hòa Tấu Tinh Hoa.</t>
+          <t>Sau một hồi nỗ lực, cậu đã cùng nhau nấu thành công món Súp Hòa Âm Tinh Hoa.</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Bạn, Chixia và Panhua cùng nhau nếm thử Món Súp Hòa Tấu Tinh Hoa.</t>
+          <t>Cậu, Chixia và Panhua cùng nhau thưởng thức món Súp Hòa Âm Tinh Hoa.</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Thật khó nói... Không hẳn là tệ, nhưng...</t>
+          <t>Nói thế nào nhỉ... Không phải là tệ, nhưng mà...</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Cũng không khá hơn. Ít nhất thì cũng còn xa mới bằng những món khác cậu nấu.</t>
+          <t>Cũng không khá hơn. Ít ra thì cũng khác xa mấy món mày nấu khác.</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Ôi không, chúng ta đã đi được đến đây rồi. Like trong một câu chuyện điển hình, đã đến lúc chúng ta tự hào tuyên bố: "Nhờ sự kiên trì, chúng ta đã khám phá ra hương vị hoàn hảo," phải không?</t>
+          <t>Ôi không, đến nước này rồi. Đúng kiểu kịch bản điển hình, giờ chúng ta phải hùng hồn tuyên bố: "Nhờ kiên trì, chúng ta đã tìm ra hương vị hoàn hảo," phải không?</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Đây có phải là một trong những bài học từ Hero Plays không?</t>
+          <t>Đây có phải là một trong những vở kịch của Hero Plays không?</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Chắc không chỉ là "bình thường" đâu.</t>
+          <t>Không hẳn là "bình thường" đâu, tớ nghĩ thế.</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Có vẻ Rover khá giỏi trong việc nấu nướng. Dù đây không phải món phức tạp, nhưng cậu đã xử lý rất chuyên nghiệp, nhất là với một đầu bếp mới vào nghề.</t>
+          <t>Có vẻ như Rover cũng khá có tay nghề trong bếp đấy. Dù đây không phải món phức tạp, nhưng cậu xử lý như dân chuyên nghiệp luôn, nhất là với một người mới tập nấu ăn.</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Không, tôi chỉ đang tập trung thôi.</t>
+          <t>Không, tôi chỉ hứng thú thôi.</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Có lẽ ta chính là Thần Nấu Ăn huyền thoại.</t>
+          <t>Biết đâu ta chính là Vị Thần Nấu Ăn huyền thoại chăng?</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Có vẻ tôi sẽ phải bắt đầu gọi cậu là thầy mất rồi.</t>
+          <t>Có vẻ ta sẽ phải gọi cậu là thầy mất thôi.</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Đó không phải là nịnh hót. Tôi có mắt mà, tôi thấy bạn xử lý từng bước rất dễ dàng.</t>
+          <t>Đây không phải nịnh hót đâu. Ta có mắt mà, thấy rõ cậu xử lý từng bước dễ dàng như chơi.</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Được rồi, sau bao nỗ lực, đã đến lúc nghỉ ngơi rồi.</t>
+          <t>Được rồi, sau bao công sức, giờ là lúc nghỉ ngơi thôi.</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Wow, cậu có tin được là chúng ta đã đi gần nửa thành Jinzhou chỉ trong một ngày không?</t>
+          <t>Ôi, không ngờ chỉ trong một ngày mà chúng ta đã đi gần nửa Jinzhou rồi nhỉ?</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Mệt thật đấy, nhưng rất đáng! Bình thường tớ bận tuần tra nên việc gặp gỡ nhiều bạn bè cùng lúc như thế này là lần đầu tiên luôn.</t>
+          <t>Mệt thì có mệt, nhưng đáng lắm chứ! Bình thường mình toàn bận tuần tra, nên được gặp mặt bao nhiêu bạn bè cùng lúc như thế này là lần đầu đấy.</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Nhưng mà, nhờ cậu, cuối cùng tớ cũng hiểu tại sao mọi người lại mê món Súp Hòa Tấu Bản Chất đến vậy.</t>
+          <t>Nhưng mà này, nhờ cậu đấy, cuối cùng mình mới hiểu tại sao mọi người lại mê Súp Bản Giao Hưởng đến thế.</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Đó mới là hương vị đích thực của Jinzhou.</t>
+          <t>Đúng là hương vị chính hiệu Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Vậy nên, khi ở Jinzhou, để tớ gánh giúp những lo âu, phiền muộn của cậu nhé, được không?</t>
+          <t>Thế nên, khi ở Jinzhou, để tôi gánh giúp những lo âu, phiền muộn của cậu nhé?</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Có vẻ tôi không thể từ chối được.</t>
+          <t>Có vẻ là ta không thể từ chối đâu.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Bạn có thể đặt cược vào quyết tâm của tay đua Jinzhou này!</t>
+          <t>Hãy đặt cược vào quyết tâm của tay đua tốc độ Jinzhou này đi!</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Sau khi đến gần Panhua's Restaurant, bạn nhắn tin cho Chixia và đợi một lúc...</t>
+          <t>Sau khi đến gần Nhà hàng Panhua, cậu nhắn tin cho Chixia và đợi một lát...</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Chào cậu, Rover! Cuối cùng cũng tìm thấy cậu! Hy vọng mình không để cậu đợi lâu!</t>
+          <t>Này, Vận Mệnh Giả! Cuối cùng cũng tìm thấy cậu! Hy vọng tớ không để cậu đợi lâu nhé!</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Cảm giác như mãi mãi không gặp. Bụng tôi sôi lên rồi đây.</t>
+          <t>Cảm giác như đã cả thế kỷ rồi ấy. Bụng mình sôi lên đến nơi rồi.</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Đừng lo. Món ngon luôn đáng để chờ đợi.</t>
+          <t>Đừng lo, đồ ngon bao giờ chẳng đáng để chờ đợi.</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>À, xin lỗi nhé! Đừng chần chừ nữa. Tin tôi đi, một khi đã ăn rồi, cậu sẽ không muốn dừng lại đâu!</t>
+          <t>À, lỗi của ta! Đừng chần chừ nữa. Tin ta đi, một khi đã nếm thử, các cậu sẽ không muốn dừng lại đâu!</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Ôi, anh thật tốt bụng, nhưng ăn uống vẫn là trên hết! Hãy bắt đầu gọi món và mở đầu bữa tiệc thôi nào!</t>
+          <t>Aww, cậu tốt bụng quá, nhưng ăn uống vẫn là trên hết! Vào đặt món ngay thôi nào, mở màn bữa tiệc nào!</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>À, xem ai đến kìa! Cô bé Xiaofang của chúng ta hôm nay dẫn theo một người bạn. Thật là vui quá!</t>
+          <t>À, này, ai đến thăm thế này! Hôm nay tiểu Phương của chúng ta dẫn theo bạn nữa. Thật là vui!</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Không, không, thím Panhua à, đừng nhắc đến cái tên đó nữa! Tôi van thím đấy!</t>
+          <t>Không, không, không, dì Panhua ơi, đừng nhắc đến cái tên đó nữa! Tớ van lạy dì đó!</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Đúng rồi! Gặp Rover đi, người bạn mới tuyệt vời của tớ! Hôm nay tớ khao nhé, nên tớ dẫn {Male=cậu ấy;Female=cô ấy} đến đây để trải nghiệm tuyệt tác ẩm thực của cậu.</t>
+          <t>Ừ, chính xác! Gặp Rover này, người bạn mới tuyệt vời của tao! Hôm nay tao khao, nên đưa {Male=him;Female=her} tới đây để thưởng thức tuyệt tác ẩm thực của các cậu.</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Ôi trời, vậy thì tớ phải cho {Male=anh ấy;Female=cô ấy} xem cái này mới được!</t>
+          <t>Ôi trời, vậy thì ta phải cho {Male=him;Female=her} xem cái này mới được!</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Bạn có sở thích hay không thích gì không? Ngọt, mặn, chua, cay, cứ cho tôi biết bạn thích gì nhé. Món ăn Jinzhou nào cũng hợp khẩu vị!</t>
+          <t>Cậu thích hay không thích món gì? Ngọt, mặn, chua, cay... cứ nói ra, ở Jinzhou luôn có món ăn hợp khẩu vị của cậu!</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Tôi thích món nhẹ nhàng, tôn lên hương vị nguyên liệu.</t>
+          <t>Ta thích thứ gì đó nhẹ nhàng, thứ tôn lên hương vị nguyên bản của nguyên liệu.</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Cay thật! Cho tôi cảm giác mạnh nào!</t>
+          <t>Cay nồng! Cho ta cảm giác mạnh nào!</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Tớ không kén chọn đâu. Chixia, cậu có gợi ý gì không?</t>
+          <t>Tao không kén chọn đâu. Chixia, có gợi ý gì không?</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Được rồi, món nhẹ nhàng thôi... Tự tìm chỗ ngồi bên trong đi. Món ăn sẽ sớm xong thôi.</t>
+          <t>Được rồi, món nhẹ nhàng thôi... Tự tìm chỗ ngồi trong này đi. Món ăn sẽ sớm xong ngay thôi.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Chẳng mấy chốc, Panhua đã dọn món lên. Sự kết hợp tuyệt vời giữa Bánh Củ Mã Thầy Đường và món Hầm Jinzhou nấu chậm khiến bạn thấy đói bụng.</t>
+          <t>Chẳng mấy chốc, Panhua đã dọn món lên. Sự hòa quyện ngọt ngào của Kẹo Hạt Củ Sen và Lẩu Jinzhou ninh nhừ khiến bụng cồn cào.</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Được rồi, món gì đó cay... Tìm chỗ ngồi bên trong đi. Món ăn sẽ sớm xong thôi.</t>
+          <t>Được rồi, món cay nè... Tự tìm chỗ ngồi trong này đi. Món ăn sẽ sớm xong ngay thôi.</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Chẳng mấy chốc, Panhua dọn món ăn lên. Món Gà Luộc Nước Sốt thơm ngon cùng Đậu Hũ Mapo cay xè lưỡi khiến bạn thèm ăn hơn.</t>
+          <t>Chẳng mấy chốc, Panhua đã dọn món lên. Món Gà Luộc Nước Mắm đậm đà, kết hợp với Đậu Hũ Mapo cay xè và tê tê khiến vị giác thức tỉnh.</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Tôi đã quyết định. Hãy lấy tất cả chúng.</t>
+          <t>Tớ quyết định rồi. Lấy hết chúng đi.</t>
         </is>
       </c>
     </row>
@@ -20529,7 +20529,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Nhiều quá... Chúng ta có làm hết được không?</t>
+          <t>Nhiều quá... Liệu chúng ta có ăn hết nổi không?</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Dù chúng tôi, Đội Tuần tra, không được trả lương cao, nhưng thỉnh thoảng tôi vẫn thích chiêu đãi bạn bè một bữa thịnh soạn. Chỉ một bữa thôi, không đến nỗi phá sản đâu!</t>
+          <t>Chúng ta, Đội Tuần Tra, lương không cao lắm, nhưng thỉnh thoảng vẫn thích đãi bạn bè một bữa tiệc. Chỉ một bữa thôi, không đến nỗi phá sản đâu!</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Được rồi, các cậu tìm chỗ ngồi bên trong đi. Món ăn sẽ sẵn sàng ngay thôi.</t>
+          <t>Được rồi, tìm chỗ ngồi đi nào. Món ăn sắp xong rồi.</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Chẳng mấy chốc, Panhua đã dọn món. Sự kết hợp hấp dẫn của Hạt Dẻ Đường, Gà Luộc Nước Sốt và Jinzhou Stew khiến bạn không thể cưỡng lại.</t>
+          <t>Chẳng mấy chốc, Panhua đã dọn món lên. Sự kết hợp hấp dẫn của Kẹo Hạt Củ Sen, Gà Luộc Nước Mắm và Lẩu Jinzhou khiến nước miếng cứ thế ứa ra.</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Rover, cậu thấy bữa ăn ngon không?</t>
+          <t>Rover, cậu ăn ngon không?</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Ừ, nó thật tuyệt vời. Chắc chắn mình sẽ quay lại lần nữa.</t>
+          <t>Ừ, hay lắm. Chắc chắn mình sẽ quay lại nữa.</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Không tệ.</t>
+          <t>Khá đấy.</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Lần này tôi muốn một thứ gì đó đặc biệt.</t>
+          <t>Lần này ta muốn một thứ gì đó đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Được rồi! Lần sau, chúng ta sẽ rủ cả Yangyang và Baizhi nữa. Càng đông càng vui mà, phải không? Nhưng lần này chúng ta nên ăn gì nhỉ?</t>
+          <t>Đúng rồi! Lần sau, chúng ta sẽ rủ cả Yangyang và Baizhi nữa. Có bạn bè thì đồ ăn ngon hơn nhiều, phải không? Nhưng lần tới mình nên ăn gì nhỉ?</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Lần sau đến, tôi sẽ mời bạn thưởng thức món Súp Hòa Tấu Bản Chất nổi tiếng của tôi.</t>
+          <t>Lần sau đến, tôi nhất định phải đãi cậu món Súp Hòa Tấu Bản Chất nổi tiếng của mình.</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Chỉ thế thôi sao? Thật á? Đến cả tài nghệ nấu nướng của Dì Panhua cũng không lay chuyển được cậu à?</t>
+          <t>Chỉ có vậy thôi á? Thật sao? Đến cả tài nghệ nấu nướng của Dì Panhua cũng không lay chuyển được cậu à?</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Có vẻ tớ sẽ phải giới thiệu cho cậu về điều kỳ diệu của món Essence Medley Soup.</t>
+          <t>Có vẻ ta sẽ phải giới thiệu cho cậu món tuyệt phẩm Essence Medley Soup đấy.</t>
         </is>
       </c>
     </row>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Có gì đặc biệt à? Hmm, cho tôi chút thời gian suy nghĩ đã.</t>
+          <t>Có gì đặc biệt à? Hmm, để tao nghĩ đã.</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Vậy thì, tôi sẽ giới thiệu cho cậu món tuyệt vời: Súp Hòa Âm Tinh Hoa.</t>
+          <t>Nếu vậy, tôi sẽ phải giới thiệu cho cậu món Essence Medley Soup tuyệt vời.</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Essence Medley Soup à? Đó là gì?</t>
+          <t>Essence Medley Soup á? Đó là gì vậy?</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Đừng bảo em định thử ngay bây giờ...</t>
+          <t>Đừng có mà bảo mày lại định thử ngay bây giờ...</t>
         </is>
       </c>
     </row>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Sao trông cậu háo hức thế?</t>
+          <t>Sao mặt cậu lại háo hức thế?</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Nghe ngon tuyệt. Tôi rất muốn tự mình nếm thử.</t>
+          <t>Nghe ngon tuyệt. Ta cũng muốn nếm thử ngay.</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Nói đến nguyên liệu kỳ lạ, quả thật làm tôi nhớ đến ai đó...</t>
+          <t>Nói về những nguyên liệu kỳ lạ, quả thật làm ta nhớ đến ai đó...</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Đừng vòng vo nữa. Nói thẳng đi. Tôi không thấy phật lòng đâu.</t>
+          <t>Đừng vòng vo nữa. Nói thẳng ra đi. Ta không giận đâu.</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>À… đó là Bác Mahe!</t>
+          <t>Ồ… hóa ra là chú Mahe!</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Hừm, ông ta cứ khoe khoang là có thể kiếm được bất kỳ nguyên liệu nào, nhưng nếu không biết mấy thứ này thì chỉ đang phí thời gian trong nghề thôi.</t>
+          <t>Hừ, lúc nào hắn cũng khoác lác là kiếm được mọi nguyên liệu, nhưng nếu chẳng biết gì về mấy thứ này thì chỉ đang phí thời gian thôi.</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Nói rõ cho cậu biết, tôi sẽ không đến hỏi anh ta đâu, nhưng nếu cậu muốn thử nghiệm công thức này với anh ta thì tùy cậu thôi.</t>
+          <t>Nói rõ cho cậu biết, tôi sẽ không đến hỏi hắn đâu, nhưng nếu cậu muốn thử nghiệm công thức này với hắn thì tùy cậu thôi.</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Dì Panhua! Dì thật là tốt bụng. Con luôn biết điều đó mà!</t>
+          <t>Dì Panhua! Dì thật là tốt bụng. Con biết mà!</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Được rồi, tôi sẽ sao chép công thức cho cậu.</t>
+          <t>Được rồi, mình sẽ chép công thức cho cậu.</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Ta sẽ cùng Chixia đi dạo quanh thành phố để làm quen với nơi này.</t>
+          <t>Ta sẽ dạo quanh thành phố cùng Chixia để làm quen với nơi này.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Khi súp nấu xong, đừng quên để chúng tôi nếm thử nhé!</t>
+          <t>Khi súp chín rồi, đừng quên để chúng ta nếm thử nhé!</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Đừng lo! Tôi sẽ không để bạn làm không công đâu! Dì đây sẽ đảm bảo bạn ăn no nê!</t>
+          <t>Đừng lo! Ta sẽ không để các ngươi làm không công đâu! Chị đây sẽ lo cho các ngươi ăn no bụng mới thôi!</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Ôi, ai đây nhỉ? Chixia, lại đi giao hàng à?</t>
+          <t>Này này, ai đấy nhỉ? Chixia, lại đi giao hàng à?</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Haha, nhưng thật lòng mình rất mang ơn cậu đã giúp đỡ. Chính nhờ cậu mà những người lớn tuổi khó đi lại mới nhận được hàng đúng giờ. Cảm ơn nhiều nhé!</t>
+          <t>Haha, nhưng thật lòng mà nói, tao nợ mày một ân huệ to đấy. Chính nhờ mày mà mấy cụ già khó đi lại mới nhận được hàng đúng giờ. Cảm ơn nhé!</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Ừ, đúng vậy... Nhưng có điều thú vị là chính dì Panhua đã cho tôi công thức này.</t>
+          <t>À, đúng vậy... Nhưng có điều thú vị là, chính dì Panhua đã cho tôi công thức này đấy.</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Gì cơ? Cô ấy gặp chuyện à? Đưa công thức đây!</t>
+          <t>Sao? Cô ấy gặp rắc rối à? Đưa công thức cho ta ngay!</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Sau khi nghe giải thích của bạn, Mahe xem xét kỹ lưỡng công thức cũ.</t>
+          <t>Sau khi nghe giải thích của cậu, Mahe xem xét kỹ công thức cũ.</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Hừm? Rõ ràng là có gì đó giữa họ!</t>
+          <t>Hừm? Rõ ràng là có gì đó giữa hai người ấy!</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Này, bác Mahe, bác có phát hiện ra điều gì không?</t>
+          <t>Này, chú Mahe, chú có phát hiện được gì không?</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>I see. Họ đang diễn cái màn "lạnh lùng nhưng thực ra quan tâm" đúng không?</t>
+          <t>Ta hiểu rồi. Họ đang diễn cái trò "lạnh lùng nhưng thực ra lại quan tâm" ấy hả?</t>
         </is>
       </c>
     </row>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Chixia, cậu có vẻ biết nhiều nhỉ.</t>
+          <t>Chixia, cậu biết nhiều thứ thật đấy.</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Ồ đúng rồi! Đúng là vậy! Không ngờ cậu lại có tài tóm tắt đến thế. Chắc cậu là fan cứng của những vở kịch anh hùng nhỉ?</t>
+          <t>Ừ nhỉ! Đúng rồi! Không ngờ cậu lại có tài tóm tắt thế. Chắc cậu là fan cứng của Hero Plays rồi, phải không?</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Thôi bỏ đi. Mối quan hệ như mạng nhện rối bời, ngay cả ta cũng không gỡ nổi!</t>
+          <t>Thôi bỏ đi. Mối quan hệ như mớ bòng bong, đến tôi còn chẳng gỡ nổi!</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Tất nhiên! Tôi như một cuốn bách khoa toàn thư về mọi thứ ở Jinzhou! Lo lắng và phiền muộn đều là một phần khi giải quyết các mối quan hệ!</t>
+          <t>Tất nhiên! Tớ như một cuốn bách khoa toàn thư sống về mọi thứ ở Jinzhou đấy! Lo lắng và phiền muộn cũng chỉ là một phần khi nói đến chuyện tình cảm thôi mà!</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>...À, mình hiểu rồi. Công thức này có vẻ khá cũ. Nó dùng những tên gọi cũ thay vì những cái tên quen thuộc với chúng ta, nên khá khó giải mã.</t>
+          <t>...À, ra vậy. Công thức này có vẻ khá cũ rồi. Nó dùng những tên gọi kiểu cũ thay vì những cái tên quen thuộc với chúng ta, nên hơi khó giải mã.</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Bác Mahe có bộ sưu tập khá ấn tượng đấy.</t>
+          <t>Chú Mã Hạ sưu tầm được kha khá đồ ở đây nhỉ.</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi! Bác Mahe là người có thể lo mọi thứ ở Jinzhou. Không chỉ nguyên liệu nấu ăn, bác ấy còn có thể kiếm được nhiều thứ kỳ lạ đấy!</t>
+          <t>Chuẩn không cần chỉnh! Bác Mahe chính là người nắm mọi thứ ở Jinzhou đấy. Không chỉ nguyên liệu nấu ăn, ông ấy còn kiếm được cả những thứ kỳ lạ nữa cơ!</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Nếu muốn mua gì, cứ thoải mái xem nhé.</t>
+          <t>Nếu cậu muốn mua gì, cứ đến xem thử đi.</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Chixia, cô quá khen rồi. Tất cả đều nhờ mọi người trong khu phố ủng hộ cửa hàng của tôi. Nếu cần gì, cứ nói nhé.</t>
+          <t>Chixia, cậu quá khen rồi. Tất cả đều là nhờ mọi người trong khu phố ủng hộ cửa hàng của tớ. Nếu cậu cần gì, cứ nói nhé.</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Ừ, mình sẽ làm.</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Cảm ơn Bác Mahe.</t>
+          <t>Cảm ơn bác Mahe.</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Ta biết mọi biệt danh của đồ ăn trong sách, và rõ ràng hai thứ này không phải nguyên liệu nấu ăn.</t>
+          <t>Ta biết mọi biệt danh đồ ăn trong sách vở, và hai thứ này rõ ràng không phải nguyên liệu nấu nướng.</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Có phải chúng ta đang nhìn sai hướng?</t>
+          <t>Chúng ta đang tìm nhầm hướng rồi phải không?</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Cảm ơn vì nguồn cảm hứng! Bác Mahe ơi, mấy nguyên liệu này bao nhiêu tiền? Cháu sẽ thanh toán.</t>
+          <t>Cảm ơn vì đã truyền cảm hứng! Chú Mahe, mấy nguyên liệu này giá bao nhiêu? Để cháu thanh toán.</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi! Nếu dì Panhua làm món này, cậu sẽ được nếm thử ngay trên hàng ghế đầu!</t>
+          <t>Chắc chắn luôn! Nếu dì Panhua làm món này, cậu sẽ được ngồi hàng đầu nếm thử đấy!</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Chúng ta đã đi từ Phố Ẩm Thực đến đây rồi. Cược là cậu chưa từng có nhiều chuyến dạo phố như thế này trước đây nhỉ?</t>
+          <t>Từ Phố Ẩm Thực đến đây, chúng ta đã đi qua không ít nơi rồi. Chắc cậu chưa từng dạo phố như thế này bao giờ nhỉ?</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Dù hơi xa xôi nhưng tôi rất háo hức dẫn bạn tham quan quê hương mình. Chúng ta sắp đến Phố Main rồi, nơi có nhiều điều thú vị hơn nữa đấy.</t>
+          <t>Dù phải đi một đoạn đường xa, nhưng tao rất háo hức được dẫn cậu tham quan quê hương mình. Chúng ta sắp đến Phố Chính rồi, nơi mà mọi thứ sẽ thú vị hơn nhiều.</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Hello, mình có thể giúp gì...? Ồ, chị Chixia à?</t>
+          <t>Xin chào, tôi có thể giúp gì... À, cô Chixia à?</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Cậu đến đây vì chuyện gì? Đi mua thuốc giùm ai à, hay là cậu thấy không khỏe? Có bị thương không? Đã đi khám bác sĩ chưa? Cần đơn thuốc gì không?</t>
+          <t>Có chuyện gì mà bạn lại đến đây? Đi lấy thuốc hộ ai à, hay là cảm thấy không khỏe? Có bị thương không? Đã đi khám bác sĩ chưa? Cần kê đơn gì không?</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Ồ, chào đón nhiệt tình quá nhỉ.</t>
+          <t>Ồ, chào đón nhiệt tình quá đi mất!</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Có vẻ cậu lo lắng cho cô ấy khá thường xuyên đấy.</t>
+          <t>Có vẻ cậu thường xuyên lo lắng cho cô ấy đấy.</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Yeah... Khoan đã! Rover, ý cậu là sao? Rõ ràng là tôi...</t>
+          <t>Ừ... Khoan đã! Rover, ý cậu là sao? Rõ ràng là mình...</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Rõ ràng là vậy đấy, giống như vị {Male=quý ông;Female=quý bà} này nói, cứ hăng quá là quên cả an toàn bản thân!</t>
+          <t>Rõ ràng như lời {Male=gentleman;Female=lady} này nói, một khi đã cuốn vào cuộc chơi, cậu sẽ quên cả sự an toàn của bản thân!</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Nghiêm túc đấy, cậu không có việc gì làm à? Ai lại đi theo dõi mấy thứ này chứ!</t>
+          <t>Nói thật đấy, không phải mày còn việc phải làm à? Ai lại đi theo dõi mấy thứ này chứ!</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Thôi không vòng vo nữa. {PlayerName} và tôi đến đây để nhờ cậu xem qua công thức mà dì Panhua đưa cho chúng tôi.</t>
+          <t>Thôi không vòng vo nữa. {PlayerName} và tôi đến đây để nhờ cậu xem thử công thức mà Dì Panhua đưa cho chúng tôi.</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Canh Essence Medley? Nghe như là món bà tôi hay thế hệ của bà ấy nấu.</t>
+          <t>Món Essence Medley Soup á? Nghe như là thứ bà mình hay nấu vậy.</t>
         </is>
       </c>
     </row>
@@ -24689,7 +24689,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Thật sao? Cố nhớ xem nào! Bác Mahe nghĩ đây giống món ăn dược liệu hơn là món ăn thông thường đấy.</t>
+          <t>Thật sao? Cố nghĩ xem nào! Bác Mahe bảo đây là món ăn dược liệu hơn là món ăn thường đấy.</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Vì chúng ta đã biết nguyên liệu cần thiết, tôi và Chixia sẽ đi lấy những thứ cần dùng.</t>
+          <t>Biết rõ nguyên liệu cần thiết rồi, tớ và Chixia sẽ đi lấy những thứ cần dùng thôi.</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Bạn có quan tâm đến liệu pháp dinh dưỡng?</t>
+          <t>Cậu có hứng thú với liệu pháp dinh dưỡng không?</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Khỏi cần phải phiền phức thế. Nhớ nơi này chứ? Nhà thuốc đấy! Tôi có sẵn mấy nồi súp thuốc chế sẵn rồi đây.</t>
+          <t>Không cần phải phiền phức thế. Nhớ nơi này là gì không? Nhà thuốc đấy! Tớ có sẵn mấy nồi súp thuốc chế sẵn rồi này.</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Thuốc đắng giã tật, nên tôi đang nghĩ cách làm cho nó dễ uống hơn.</t>
+          <t>Thuốc đắng thì mới dã tật, nên tớ đang nghĩ cách làm nó dễ uống hơn.</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Bằng cách chế biến thành món ăn dược liệu, chúng ta giữ lại đặc tính chữa bệnh đồng thời loại bỏ vị đắng, để ai cũng có thể thưởng thức ngon miệng.</t>
+          <t>Chế biến thành món ăn dưỡng sinh, ta vừa giữ được dược tính vừa loại bỏ vị đắng, để ai cũng có thể thưởng thức ngon miệng.</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Công thức này có vẻ cổ xưa. "Nước Monkvyrid" là thuật ngữ cũ trong dược điển, chỉ loại súp thuốc đó. Khoan đã, tôi có sẵn nguyên liệu pha chế sẵn cho bạn đây.</t>
+          <t>Công thức này có vẻ cổ xưa lắm. "Nước Monkvyrid" là thuật ngữ cũ trong dược điển, chỉ loại canh thuốc đó. Khoan đã, tôi có sẵn nguyên liệu pha chế cho cậu đây.</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>À, và đây là vài bình thuốc hồi phục và tổng hợp mới. Coi như quà tặng thêm.</t>
+          <t>À, và đây là mấy bình thuốc hồi phục và tổng hợp mới. Coi như quà tặng thêm nhé.</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Dù có thuốc trị thương, hãy cẩn thận ngoài kia nhé? Luôn cảnh giác khi khám phá.</t>
+          <t>Nhưng dù có thuốc trị thương đi chăng nữa, cậu vẫn phải cẩn thận ngoài kia nhé? Luôn đề cao cảnh giác khi khám phá đấy.</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Đừng có mà học theo Chixia, xông vào làm mọi người sợ hết hồn.</t>
+          <t>Đừng có học theo Chixia, xông vào làm mọi người hết hồn như thế.</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Cảm ơn đã nhắc tôi.</t>
+          <t>Cảm ơn cậu đã nhắc tớ.</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Tin tôi đi. Tôi sẽ không làm đâu.</t>
+          <t>Tin tớ đi. Tớ sẽ không làm đâu.</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Thật sự à? Danh tiếng "Tay Đua Tốc Độ Jinzhou" của tôi...</t>
+          <t>Cậu nghiêm túc đấy à? Danh tiếng "Tay Đua Tốc Độ Jinzhou" của tôi...</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Vậy là hai người định quay về giúp dì Panhua nấu món Essence Medley Soup à? Nếu vậy, cho tôi học luôn công thức đó với nhé!</t>
+          <t>Vậy, hai cậu định về giúp dì Panhua nấu món Essence Medley Soup à? Nếu thế, cho tớ học ké công thức luôn nhé!</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Cứ báo với dì Panhua nhé. Chắc chắn cậu tham gia được mà!</t>
+          <t>Cứ báo với dì Panhua là được! Dì sẽ lo cho cậu tham gia mà!</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Khoan, cái muỗng cán vàng này chẳng phải cái muỗng pyrite to đùng ở tiệm chú Vi sao? Tớ tưởng hai cậu biết mà.</t>
+          <t>Chờ đã, cái muỗng cán vàng đó chẳng phải cái muỗng pyrite to đùng của chú Wei à? Tớ tưởng cả hai cậu đều biết mà.</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Câu trả lời đã ở ngay trước mắt chúng ta từ đầu.</t>
+          <t>Câu trả lời đã ở ngay trước mắt chúng ta từ đầu rồi.</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>That makes sense... Dù sao thì pyrite cũng được gọi là vàng của kẻ ngốc mà.</t>
+          <t>Hợp lý thật... Rốt cuộc thì pyrite cũng chỉ là vàng của kẻ ngốc thôi.</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Ôi, có vẻ tôi phải từ bỏ vai trò "bách khoa toàn thư Jinzhou" rồi. Tôi còn chưa nghe qua cái muỗng pyrite này bao giờ!</t>
+          <t>Ôi, có vẻ tôi phải từ bỏ danh hiệu "bách khoa toàn thư Jinzhou" mất rồi. Tôi còn chưa nghe tới cái muỗng pyrite này bao giờ!</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Haha, không sao đâu. Lần trước tôi mang thuốc đến cho chú Wei, tình cờ thấy chiếc muỗng đó nên hỏi thử thôi.</t>
+          <t>Haha, không sao đâu. Tao thấy cái muỗng đó lần trước giao thuốc cho chú Wei nên tò mò hỏi thôi.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Xem kìa. Đó là cửa hàng vũ khí của chú Wei đằng kia.</t>
+          <t>Nhìn kìa. Đó là cửa hàng vũ khí của chú Wei đằng kia.</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Anh ấy là thợ rèn vũ khí hàng đầu ở Jinzhou! Nếu có thắc mắc gì về vũ khí, cứ hỏi anh ấy.</t>
+          <t>Ông ấy là thợ rèn vũ khí hàng đầu ở Jinzhou đấy! Nếu có thắc mắc gì về vũ khí, cứ đến hỏi ông ấy.</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Việc bảo dưỡng vũ khí của cậu thế nào rồi? Khi nào tìm ra được chuyện cái muỗng lớn kia, cậu có thể nhờ hắn kiểm tra giúp!</t>
+          <t>Bảo dưỡng vũ khí của cậu thế nào rồi? Khi nào tìm ra bí mật cái muỗng lớn kia, cậu có thể nhờ ông ấy kiểm tra luôn cho!</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Ôi, lại là Xiaofang của ta à. Quay lại sớm thế? Tuần trước ta mới sửa đôi súng cho cậu xong, giờ lại hỏng rồi à?</t>
+          <t>Ồ, Xiaofang của chúng ta đây rồi. Về sớm thế? Tao mới sửa súng cho mày tuần trước mà, lại hỏng rồi à?</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>...Ôi, đừng gọi tôi là Tiểu Phương nữa! Là Xích Hà cơ!</t>
+          <t>...Ôi, đừng gọi tớ là Xiaofang nữa! Là Chixia cơ mà!</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Ôi không, ta tiêu rồi. Có vẻ như giờ ai cũng biết tên khác của ta rồi.</t>
+          <t>Ôi không, mình tiêu rồi. Hình như giờ ai cũng biết tên khác của mình rồi.</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Haha, cậu nói quá rồi. Theo tôi biết, chỉ có đám bạn cũ của cậu mới gọi cậu như thế thôi.</t>
+          <t>Haha, cậu nói quá rồi. Theo tao biết, chỉ có tụi tao, mấy người bạn cũ của cậu, mới gọi cậu như thế thôi.</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Uncle Wei, đừng trêu cô ấy nữa.</t>
+          <t>Chú Vi, đừng trêu cháu ấy nữa.</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Giờ thì tôi hiểu rồi, Xiaofang.</t>
+          <t>Hiểu rồi, Tiểu Phương.</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Tốt, tốt. Vậy thì bắt đầu thôi.</t>
+          <t>Tuyệt, tuyệt. Vậy thì bắt tay vào việc thôi.</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>{PlayerName}, đến cậu cũng thế à?! Không, đừng... Giữ bí mật tên đó giữa chúng ta thôi nhé?</t>
+          <t>{PlayerName}, cậu cũng thế à?! Không, đừng nói nữa... Giữ bí mật tên đó giữa chúng ta thôi nhé?</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Dù sao thì, chúng ta đến đây để giúp Dì Panhua nấu lại món Canh Hòa Âm Tinh Hoa.</t>
+          <t>Dù sao thì, tụi tớ đến đây để giúp dì Panhua nấu lại món Canh Hòa Tấu Tinh Hoa.</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>À, ra vậy.</t>
+          <t>À, vậy à.</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Một món ăn dược liệu bí truyền.</t>
+          <t>Một món ăn dược phẩm bí truyền.</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Một món súp hải sản.</t>
+          <t>Một bát súp hải sản.</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Chỉ là một loại nước sắc thảo dược đơn giản thôi. Theo ta thì khó lòng gọi là ẩm thực dược liệu được.</t>
+          <t>Chỉ là một loại trà thảo mộc đơn giản thôi. Theo ta thì khó mà gọi là ẩm thực dược liệu được.</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Chà, tôi không nghĩ đây là một món ăn chính thống, vì chúng ta chỉ việc Dodgem đại một đống nguyên liệu vào với nhau thôi mà.</t>
+          <t>Thì ta không nghĩ đây là món ăn chính thống đâu, vì chúng ta chỉ ném đại mấy nguyên liệu vào với nhau thôi mà.</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Haha, cậu nói đúng. Đúng là một món chowder, nhưng không phải loại bình thường đâu.</t>
+          <t>Haha, cậu nói đúng. Đúng là món chowder thật, nhưng không phải loại bình thường đâu.</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Vậy là đây chính là món Essence Medley Soup đích thực.</t>
+          <t>Vậy đây chính là món Canh Hòa Tấu Bản Sắc thật sự.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Vậy đó là công thức thật.</t>
+          <t>Vậy đây mới là công thức thật.</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Chẳng trách dì Panhua nói rằng nó được truyền miệng qua nhiều thế hệ, khiến mọi người tranh cãi về hương vị của nó.</t>
+          <t>Thảo nào dì Panhua bảo món này truyền miệng từ đời này sang đời khác, khiến bao người tranh cãi về hương vị.</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Công thức này giống một danh sách mua sắm hơn là hướng dẫn chi tiết.</t>
+          <t>Công thức này giống danh sách mua sắm hơn là hướng dẫn chi tiết ấy nhỉ.</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Tôi biết chắc là nó ngon.</t>
+          <t>Tớ biết chắc là nó ngon lắm.</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Liệu có thực sự ngon không nhỉ?</t>
+          <t>Nó có thực sự ngon không nhỉ?</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi! Mọi nhà đều đem ra những nguyên liệu bí mật nhất để nấu món súp này. Chắc chắn là ngon tuyệt cú mèo.</t>
+          <t>Chuẩn không cần chỉnh! Mọi nhà đều đem hết nguyên liệu bí mật ra nấu món súp này. Chắc chắn phải là tuyệt phẩm rồi.</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Giờ thì tôi càng háo hức muốn nếm thử hơn, khi biết được câu chuyện đằng sau! Bác Vệ à, cho chúng tôi mượn chiếc muôi pyrite lớn của bác nhé?</t>
+          <t>Biết được câu chuyện đằng sau rồi, tao lại càng háo hức muốn nếm thử! Chú Wei, cho bọn tao mượn cái muỗng pyrite to đùng của chú đi?</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Lý do muỗng ảnh hưởng đến hương vị súp là vì nó giải phóng một số khoáng chất khi khuấy. Bạn có thể sử dụng muỗng pyrite nhỏ hơn thay thế.</t>
+          <t>Lý do thìa làm thay đổi hương vị súp là vì nó giải phóng một ít khoáng chất khi khuấy. Cậu có thể dùng thìa pyrite nhỏ hơn thay thế.</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Cũng hợp lý... À này, dì Panhua không phải đã có sẵn một cái rồi sao?</t>
+          <t>Hợp lý thật... À mà này, dì Panhua không phải đã có sẵn một cái dự phòng rồi sao?</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Đã đến đây rồi, mình tận dụng luôn nhé. Bạn giúp mình xem thử vũ khí của bạn mình được không?</t>
+          <t>Đã đến đây rồi, tranh thủ luôn đi. Giúp ta kiểm tra vũ khí của bạn ta một chút được không?</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>À, tôi nhớ ra rồi. Bạn mới đến Jinzhou phải không? Bạn là... đó...</t>
+          <t>À, tôi nhớ ra rồi. Cậu mới đến Jinzhou phải không? Cậu là... là...</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Đúng vậy. Quý bà Magistrate có nhắc đến anh là khách của Jinzhou.</t>
+          <t>Đúng vậy. Quản Sự nói cậu là khách quý của Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Để xem vũ khí của cậu nào... Hừm, vết mòn này... Không thể để mấy đứa trẻ như cậu đi lang thang với vũ khí trong tình trạng này được.</t>
+          <t>Để ta xem vũ khí của cậu... Hừm, vết mòn này... Không thể để mấy đứa trẻ như cậu đi lang thang với vũ khí trong tình trạng này được.</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Tôi thấy áy náy khi lấy chúng...</t>
+          <t>Tao thấy tội khi phải lấy chúng đi...</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Cảm ơn rất nhiều.</t>
+          <t>Cảm ơn cậu rất nhiều.</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Cháu à, vật liệu sinh ra để dùng. Nếu muốn cảm ơn ta, hãy dùng chúng thật tốt đi.</t>
+          <t>Cháu à, vật liệu sinh ra là để dùng. Nếu muốn cảm ơn bác, hãy tận dụng chúng thật tốt.</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Ừm, vũ khí này trông cũng tạm được. Hãy giữ gìn nó nhé?</t>
+          <t>Ừm, vũ khí này trông cũng khá ổn đấy. Cậu giữ gìn nó cẩn thận nhé?</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Cảm ơn Bác Wei.</t>
+          <t>Cảm ơn chú Vệ.</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Không cần khách sáo thế đâu, nhóc. Tôi cũng chẳng làm được gì ngoài việc cậu mò vũ khí thôi.</t>
+          <t>Đừng khách sáo thế, nhóc. Tôi chẳng giúp được gì nhiều ngoài việc mày mò vũ khí thôi.</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Cho cậu biết thôi, quặng và vật liệu tớ vừa đưa không phải loại tốt nhất đâu. Muốn đồ chất lượng cao hơn thì cậu nên ghé Máy Tổng hợp nhé.</t>
+          <t>Cậu biết đấy, quặng và nguyên liệu tớ vừa đưa không phải loại tốt nhất đâu. Muốn hàng chất lượng hơn thì phải tìm đến Synthesizer nhé.</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Ồ, tôi có nghe nói về nó! Đó là một loại thiết bị mới mà Học viện giới thiệu vài năm trước, ở đằng kia!</t>
+          <t>À, mình có nghe rồi! Đó là một loại thiết bị mới mà Học viện giới thiệu mấy năm trước, phải không, ở đằng kia ấy!</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Thế, vì cậu biết chỗ rồi, để Chixia dẫn cậu đến đó nhé? Nếu thiếu vật liệu, tớ có thể...</t>
+          <t>Thôi được, cậu biết chỗ rồi thì để Chixia dẫn đường cho nhé? Nếu thiếu nguyên liệu thì tôi có thể...</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Ê, đừng lo, chú Wei. Gần đây cháu vừa kiếm được vài nguyên liệu tổng hợp. Rover có thể mượn của cháu!</t>
+          <t>Ê, đừng lo bác Wei ơi. Gần đây cháu vừa kiếm được mấy nguyên liệu tổng hợp này. Rover cứ lấy của cháu mà dùng!</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Xin chào, {PlayerName}.</t>
+          <t>Chào {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Xin chào, Bác Fu.</t>
+          <t>Chào chú Fu.</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Hello, còn bạn là…?</t>
+          <t>Xin chào, cậu là…?</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Haha, {Male=chàng trai;Female=cô gái} trẻ thật lễ phép.</t>
+          <t>Haha, đúng là một {Male=lad;Female=lass} lịch thiệp.</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Tôi là người đã chứng kiến Hongzhen phát triển đến ngày hôm nay trước khi giao lại cho Xinyi.</t>
+          <t>Ta là người đã chứng kiến Hongzhen phát triển đến ngày hôm nay trước khi giao lại cho Xinyi.</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Thôi, chuyện cũ để lại quá khứ đi… Cứ gọi tôi là Bác Phú thôi.</t>
+          <t>Ôi, quá khứ hãy để nó qua đi... Cứ gọi ta là chú Phú thôi.</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Bạn nghĩ sao về Hongzhen dạo này?</t>
+          <t>Vậy thì cậu nghĩ sao về Hongzhen dạo này?</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Có gì đó đang được chuẩn bị.</t>
+          <t>Có gì đó đang sôi sục rồi.</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Những ngày tốt đẹp đang đến.</t>
+          <t>Ngày mai sẽ tươi sáng hơn thôi.</t>
         </is>
       </c>
     </row>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>À, cậu lạc quan thật đấy, cháu ơi.</t>
+          <t>À, cậu lạc quan quá nhỉ, tiểu tử à.</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Ngươi đã thấy cuộc khủng hoảng ở Núi Hiên Viên, vậy mà không sợ sao?</t>
+          <t>Mày đã thấy cuộc khủng hoảng ở Núi Firmament mà vẫn không sợ à?</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Bạn làm tôi nhớ đến Xinyi lần đầu tôi gặp cô ấy.</t>
+          <t>Cậu khiến ta nhớ đến Xinyi lần đầu ta gặp cô ấy.</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Cả hai các bạn đều là những người đã trải qua thời loạn lạc và vẫn đứng vững trước mọi nghịch cảnh.</t>
+          <t>Cả hai ngươi đều là những người đã sống sót qua thời loạn lạc và vẫn đứng vững trước mọi nghịch cảnh.</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Xin lỗi, tớ đã mất kiểm soát. Tớ muốn gặp cậu vì có thứ muốn trao cho cậu.</t>
+          <t>Xin hãy tha thứ, ta đã mất kiểm soát. Ta muốn gặp ngươi vì có thứ muốn trao cho ngươi.</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Bác Phúc lấy ra một vật giống chiếc cân và trao cho bạn một cách trịnh trọng.</t>
+          <t>Chú Phú lấy ra một vật giống như chiếc vảy và trao cho cậu một cách trịnh trọng.</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Của cậu đây.</t>
+          <t>Cậu đến rồi.</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Đây là…?</t>
+          <t>Cái này… là gì?</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Khi tôi mới trở thành Thị Trưởng Hongzhen, tôi tình cờ tìm thấy thứ này trong một lần đi dạo trên núi.</t>
+          <t>Lần đầu tao nhậm chức Thị Trưởng Hongzhen, tao tình cờ thấy thứ này trong một lần đi dạo trên núi.</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Ban đầu, tôi bị thu hút bởi hình dạng kỳ lạ của nó nên đã mang về thị trấn. Nhưng sau đó, nó đã bộc lộ một sức mạnh thực sự đáng kinh ngạc.</t>
+          <t>Ban đầu, tao tò mò vì hình dáng kỳ lạ của nó nên mang về thị trấn. Nhưng sau đó, nó lại bộc lộ một sức mạnh thực sự đáng kinh ngạc.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Có chuyện gì vậy?</t>
+          <t>Sao thế?</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Nó có thể quay ngược thời gian không?</t>
+          <t>Nó có thể quay ngược thời gian thật à?</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Ừm, không hẳn... Nghe này, tôi có thể già rồi, nhưng tôi luôn để mọi thứ diễn ra tự nhiên.</t>
+          <t>Không hẳn... Nghe này, già rồi nhưng mình vẫn để mọi thứ thuận theo tự nhiên thôi.</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Con người già đi và chết đi, ngay cả ở Hồng Trấn. Sức mạnh của Sentinel chỉ có thể làm chậm thời gian chứ không thể đảo ngược nó.</t>
+          <t>Dù ở Hongzhen, con người vẫn già đi và chết đi. Sức mạnh của Người Canh Gác chỉ có thể làm chậm thời gian, chứ không thể đảo ngược nó.</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30539,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tấm vảy này—dường như nó đã đóng băng Hongzhen trong một khoảnh khắc thời gian.</t>
+          <t>Tấm vảy này... dường như đã đóng băng Hongzhen trong một khoảnh khắc thời gian.</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Vài đêm sau khi tìm thấy nó, mình mơ về khoảnh khắc mình nhặt nó lên.</t>
+          <t>Vài đêm sau khi tìm thấy nó, tao mơ về khoảnh khắc mình nhặt nó lên.</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Giấc mơ ấy chân thật như cuộc sống. Tôi thậm chí còn nhìn thấy rõ từng bông tuyết rơi—như thể thời gian đã đóng băng.</t>
+          <t>Giấc mơ ấy chân thật như đời thực. Ta thậm chí còn nhìn thấy rõ từng bông tuyết rơi—như thể thời gian đã ngừng trôi.</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Amazing.</t>
+          <t>Tuyệt.</t>
         </is>
       </c>
     </row>
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Ừ, tôi cũng hào hứng bất ngờ như cậu vậy.</t>
+          <t>Ừ, tao cũng hứng khởi vì bất ngờ y như cậu vậy.</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Tôi cứ quay lại đó suốt nửa tháng trời cho đến khi nhận ra đêm đó không phải là giấc mơ.</t>
+          <t>Tao đã quay lại đó suốt nửa tháng trời cho đến khi nhận ra đêm đó mình không hề nằm mơ.</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Dù nhỏ bé, vảy này chứa đựng sức mạnh không thể tưởng tượng. Khi tôi mang nó, nó ghi lại những trải nghiệm của tôi và cho phép tôi sống lại chúng sau này.</t>
+          <t>Dù nhỏ bé, chiếc vảy này chứa đựng sức mạnh không thể tưởng tượng. Khi mang nó bên mình, nó ghi lại những trải nghiệm của ta và cho phép ta sống lại chúng sau này.</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>"Khả năng này tôi gọi là 'Dấu Vết Thời Gian'. Với nó, tôi có thể thấy và nghe mọi thứ mình đã trải qua trước đây, thậm chí trò chuyện với những người đó trong Dấu Vết Thời Gian…"</t>
+          <t>Ta gọi kỹ năng này là "Dấu Vết Thời Gian". Với nó, ta có thể nhìn thấy và nghe lại mọi thứ ta đã trải qua, thậm chí còn trò chuyện với những người trong Dấu Vết Thời Gian…</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Tôi dùng khả năng này để ghi lại mọi chi tiết ở Hồng Trấn. Điều đó giúp việc biên soạn &lt;i&gt;Hồng Trấn Ký Sự&lt;/i&gt; dễ dàng hơn rất nhiều.</t>
+          <t>Ta đã dùng khả năng này để ghi lại từng chi tiết ở Hongzhen. Điều đó chắc chắn đã giúp việc biên soạn &lt;i&gt;Hongzhen Ký Sự&lt;/i&gt; dễ dàng hơn rất nhiều.</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Ban ngày, tôi lục lọi kho lưu trữ và thăm hỏi cư dân. Ban đêm, tôi dùng vật phẩm kỳ diệu này để sắp xếp thông tin đã thu thập.</t>
+          <t>Ban ngày, ta lục tìm kho lưu trữ và thăm hỏi dân cư. Đêm đến, ta dùng chiếc thẻ thần kỳ này để sắp xếp lại những thông tin đã thu thập.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Khi mình đang bận bịu với công việc quản lý... mình không thể tưởng tượng nổi mình sẽ làm việc chính thức tồi tệ thế nào nếu không có sự trợ giúp của nó.</t>
+          <t>Trong lúc ngập đầu trong công việc quản lý... ta không thể tưởng tượng nổi mình sẽ tệ hại thế nào nếu thiếu sự trợ giúp của nó.</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>...Tôi thật sự có thể nhận nó sao?</t>
+          <t>...Tôi thực sự được lấy nó sao?</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Hay là đưa nó cho Xinyi nhỉ?</t>
+          <t>Hay là nên đưa nó cho Xinyi thì hơn?</t>
         </is>
       </c>
     </row>
@@ -31449,7 +31449,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Sao cậu không giữ nó cho mình?</t>
+          <t>Sao cậu không giữ nó cho riêng mình?</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Hahaha, trước khi tôi trả lời câu hỏi của cậu, để tôi hỏi cậu một câu đã.</t>
+          <t>Hahaha, trước khi tao trả lời câu hỏi của mày, để tao hỏi mày một câu đã.</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Đoán xem tớ ghi lại được nhiều nhất điều gì với cái cân này?</t>
+          <t>Đoán xem tao ghi lại được nhiều nhất thứ gì bằng cái cân này?</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Những sự kiện quan trọng.</t>
+          <t>Sự kiện quan trọng.</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Ban đầu, tôi chỉ dùng nó cho những sự kiện quan trọng. Nhưng theo thời gian, tôi đã thay đổi cách sử dụng nó.</t>
+          <t>Lúc đầu, tao chỉ dùng nó cho những sự kiện quan trọng. Nhưng thời gian trôi qua, tao đã thay đổi cách sử dụng nó.</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Đúng vậy. Sau khi tôi từ chức Thị trưởng Hongzhen, tôi không còn can dự vào chuyện của Hongzhen nữa.</t>
+          <t>Cậu nói đúng. Sau khi tôi từ chức Thị trưởng Hongzhen, tôi không còn can dự vào chuyện của Hongzhen nữa.</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Khi tôi bàn giao vị trí cho Xinyi, tôi cũng đã trao chiếc vảy này cho cô ấy.</t>
+          <t>Khi giao lại vị trí cho Xinyi, tao cũng đưa vảy này cho cô ấy luôn.</t>
         </is>
       </c>
     </row>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Nhưng cô ấy khá chu đáo và nhanh chóng trả lại cho tôi.</t>
+          <t>Nhưng cô ấy là người chu đáo, nên chẳng bao lâu đã trả lại cho tôi.</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Vì cô ấy thấy tôi cần nó hơn. Thay vì dùng nó để lưu trữ những chi tiết vụn vặt trong công việc, cô ấy cho phép tôi ghi lại những người tôi trân trọng.</t>
+          <t>Vì cô ấy thấy tôi cần nó hơn. Thay vì dùng nó để lưu trữ những chi tiết vụn vặt trong công việc của mình, cô ấy đã để tôi ghi lại những người tôi trân trọng.</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Tôi đã chứng kiến nhiều đứa trẻ ở Hongzhen lớn lên và rời đi.</t>
+          <t>Tớ đã chứng kiến biết bao đứa trẻ ở Hongzhen lớn lên rồi rời đi.</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Ban đầu, tôi nghĩ họ sẽ quay lại vào một ngày nào đó, nhưng rồi tôi nhận ra sẽ không bao giờ gặp lại nhiều người trong số họ nữa.</t>
+          <t>Ban đầu, tao cứ nghĩ họ sẽ quay lại vào một ngày nào đó, nhưng rồi tao nhận ra sẽ chẳng bao giờ gặp lại nhiều người trong số họ nữa.</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Những năm qua, ta thực sự nhớ những người trẻ đã rời Núi Firmament để bắt đầu cuộc sống mới.</t>
+          <t>Nhiều năm qua, tôi thực sự nhớ những đứa trẻ đã rời Núi Thiên Cung để bắt đầu cuộc sống mới.</t>
         </is>
       </c>
     </row>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Vậy nên, tôi đã dùng chiếc cân để tạo Chrono Trace cho gần như mọi cư dân ở Hồng Trấn.</t>
+          <t>Thế nên, tớ đã dùng chiếc vảy này để tạo Dấu Thời Gian cho gần như tất cả cư dân ở Hồng Chẩn.</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Mỗi khi nhớ họ, tôi lại đến thăm và trò chuyện với họ trong những Dấu Vết Thời Gian đó.</t>
+          <t>Mỗi khi nhớ họ, tao lại đến thăm và trò chuyện với họ qua những Dấu Vết Thời Gian ấy.</t>
         </is>
       </c>
     </row>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Bác Fu à…</t>
+          <t>Chú Phúc à…</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Được rồi, đủ nói về mình rồi. Hãy nói về bạn đi, {PlayerName}?</t>
+          <t>Thôi nào, nói về mình đủ rồi. Giờ nói về cậu đi, {PlayerName}?</t>
         </is>
       </c>
     </row>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Có gì đó mách bảo tôi rằng chiếc vảy này có liên quan đến Jué.</t>
+          <t>Tao nghĩ cái vảy này có liên quan đến Jué.</t>
         </is>
       </c>
     </row>
@@ -32619,7 +32619,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Hồi đó, tôi cứ nghĩ Hồng Trấn cần Tâm Nghi hơn tôi, cũng như Jinhsi cần Quyết vậy.</t>
+          <t>Hồi đó, tôi nghĩ Hongzhen cần Xinyi hơn là cần tôi, giống như Jinhsi cần Jué vậy.</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Tôi đã gắn bó cả cuộc đời với thị trấn này, nhưng còn {PlayerName}, cậu không bị ràng buộc với Hongzhen hay thậm chí cả Huanglong.</t>
+          <t>Tôi đã gắn bó cả cuộc đời với thị trấn này, nhưng còn cậu, {PlayerName}, cậu không bị ràng buộc với Hongzhen hay thậm chí là Huanglong.</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Có cả một thế giới rộng lớn ngoài kia đang chờ bạn khám phá và vô số tâm hồn thú vị để kết nối.</t>
+          <t>Ngoài kia là cả một thế giới rộng lớn đang chờ cậu khám phá, và biết bao linh hồn thú vị để kết nối.</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Cậu cần chiếc vảy này hơn tôi... Hay đúng hơn, hai người hợp nhau thật đấy.</t>
+          <t>Cậu cần chiếc vảy này hơn tớ... Hay nói đúng hơn, hai người hợp nhau thật đấy.</t>
         </is>
       </c>
     </row>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Cậu có thể cho nó những Dấu Vết Thời Gian mà tôi không thể, những khoảnh khắc thực sự quan trọng.</t>
+          <t>Cậu có thể trao cho nó những Dấu Vết Thời Gian mà tôi không thể, những khoảnh khắc thực sự quan trọng.</t>
         </is>
       </c>
     </row>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Cảm ơn Bác Fu.</t>
+          <t>Cảm ơn chú Phúc.</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Tôi sẽ tận dụng tốt nó.</t>
+          <t>Tớ sẽ tận dụng tốt món này.</t>
         </is>
       </c>
     </row>
